--- a/results/simulation_workbook.xlsx
+++ b/results/simulation_workbook.xlsx
@@ -183,12 +183,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Pareto'!$A$2:$A$154</f>
+              <f>'Pareto'!$A$2:$A$131</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Pareto'!$B$2:$B$154</f>
+              <f>'Pareto'!$B$2:$B$131</f>
             </numRef>
           </yVal>
         </ser>
@@ -2284,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2317,2143 +2317,1821 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119431734</v>
+        <v>126809087</v>
       </c>
       <c r="B2" t="n">
-        <v>111827912091</v>
+        <v>113609173389</v>
       </c>
       <c r="C2" t="n">
-        <v>936.3</v>
+        <v>895.9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5609</v>
+        <v>0.5698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126809087</v>
+        <v>141510287</v>
       </c>
       <c r="B3" t="n">
-        <v>113609173389</v>
+        <v>117102310353</v>
       </c>
       <c r="C3" t="n">
-        <v>895.9</v>
+        <v>827.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5698</v>
+        <v>0.5874</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134132934</v>
+        <v>155225557</v>
       </c>
       <c r="B4" t="n">
-        <v>115321049055</v>
+        <v>119711552979</v>
       </c>
       <c r="C4" t="n">
-        <v>859.8</v>
+        <v>771.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5785</v>
+        <v>0.6005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141510287</v>
+        <v>185974063</v>
       </c>
       <c r="B5" t="n">
-        <v>117102310353</v>
+        <v>124297402813</v>
       </c>
       <c r="C5" t="n">
-        <v>827.5</v>
+        <v>668.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5874</v>
+        <v>0.6235000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>150564713</v>
+        <v>200675263</v>
       </c>
       <c r="B6" t="n">
-        <v>117968537949</v>
+        <v>127790539777</v>
       </c>
       <c r="C6" t="n">
-        <v>783.5</v>
+        <v>636.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5916</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>155225557</v>
+        <v>202526199</v>
       </c>
       <c r="B7" t="n">
-        <v>119711552979</v>
+        <v>127799592764</v>
       </c>
       <c r="C7" t="n">
-        <v>771.2</v>
+        <v>631</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6005</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>165265913</v>
+        <v>202925265</v>
       </c>
       <c r="B8" t="n">
-        <v>121461674913</v>
+        <v>127847560026</v>
       </c>
       <c r="C8" t="n">
-        <v>734.9</v>
+        <v>630</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6092</v>
+        <v>0.6412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>178596710</v>
+        <v>203372203</v>
       </c>
       <c r="B9" t="n">
-        <v>122516141515</v>
+        <v>127905546737</v>
       </c>
       <c r="C9" t="n">
-        <v>686</v>
+        <v>628.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6145</v>
+        <v>0.6415</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>178981183</v>
+        <v>204442342</v>
       </c>
       <c r="B10" t="n">
-        <v>124070917539</v>
+        <v>128050802262</v>
       </c>
       <c r="C10" t="n">
-        <v>693.2</v>
+        <v>626.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6223</v>
+        <v>0.6423</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>185974063</v>
+        <v>205684188</v>
       </c>
       <c r="B11" t="n">
-        <v>124297402813</v>
+        <v>128266593257</v>
       </c>
       <c r="C11" t="n">
-        <v>668.4</v>
+        <v>623.6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6434</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>189359634</v>
+        <v>214390533</v>
       </c>
       <c r="B12" t="n">
-        <v>124623897519</v>
+        <v>130399782403</v>
       </c>
       <c r="C12" t="n">
-        <v>658.1</v>
+        <v>608.2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6251</v>
+        <v>0.6542</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>193297910</v>
+        <v>214867542</v>
       </c>
       <c r="B13" t="n">
-        <v>126009278479</v>
+        <v>130921663758</v>
       </c>
       <c r="C13" t="n">
-        <v>651.9</v>
+        <v>609.3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6321</v>
+        <v>0.6567</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>195148846</v>
+        <v>217227399</v>
       </c>
       <c r="B14" t="n">
-        <v>126018331466</v>
+        <v>131292729728</v>
       </c>
       <c r="C14" t="n">
-        <v>645.8</v>
+        <v>604.4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6321</v>
+        <v>0.6586</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>195547912</v>
+        <v>217626465</v>
       </c>
       <c r="B15" t="n">
-        <v>126066298727</v>
+        <v>131340696989</v>
       </c>
       <c r="C15" t="n">
-        <v>644.7</v>
+        <v>603.5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6323</v>
+        <v>0.6588000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>195994850</v>
+        <v>218073403</v>
       </c>
       <c r="B16" t="n">
-        <v>126124285438</v>
+        <v>131398683700</v>
       </c>
       <c r="C16" t="n">
-        <v>643.5</v>
+        <v>602.5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>197064989</v>
+        <v>219143542</v>
       </c>
       <c r="B17" t="n">
-        <v>126269540964</v>
+        <v>131543939226</v>
       </c>
       <c r="C17" t="n">
-        <v>640.8</v>
+        <v>600.3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6333</v>
+        <v>0.6598000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>198306835</v>
+        <v>225163814</v>
       </c>
       <c r="B18" t="n">
-        <v>126485331958</v>
+        <v>132003682349</v>
       </c>
       <c r="C18" t="n">
-        <v>637.8</v>
+        <v>586.3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6344</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>200675263</v>
+        <v>226114365</v>
       </c>
       <c r="B19" t="n">
-        <v>127790539777</v>
+        <v>132129734750</v>
       </c>
       <c r="C19" t="n">
-        <v>636.8</v>
+        <v>584.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.641</v>
+        <v>0.6627</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202526199</v>
+        <v>226680891</v>
       </c>
       <c r="B20" t="n">
-        <v>127799592764</v>
+        <v>132206924585</v>
       </c>
       <c r="C20" t="n">
-        <v>631</v>
+        <v>583.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.641</v>
+        <v>0.6631</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>202925265</v>
+        <v>227312096</v>
       </c>
       <c r="B21" t="n">
-        <v>127847560026</v>
+        <v>132291113766</v>
       </c>
       <c r="C21" t="n">
-        <v>630</v>
+        <v>582</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6412</v>
+        <v>0.6635</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>203372203</v>
+        <v>229439814</v>
       </c>
       <c r="B22" t="n">
-        <v>127905546737</v>
+        <v>132625957817</v>
       </c>
       <c r="C22" t="n">
-        <v>628.9</v>
+        <v>578</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6415</v>
+        <v>0.6652</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>204442342</v>
+        <v>230942668</v>
       </c>
       <c r="B23" t="n">
-        <v>128050802262</v>
+        <v>133901972355</v>
       </c>
       <c r="C23" t="n">
-        <v>626.3</v>
+        <v>579.8</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6423</v>
+        <v>0.6717</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>205684188</v>
+        <v>231341734</v>
       </c>
       <c r="B24" t="n">
-        <v>128266593257</v>
+        <v>133949939616</v>
       </c>
       <c r="C24" t="n">
-        <v>623.6</v>
+        <v>579</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6434</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>207490189</v>
+        <v>231788672</v>
       </c>
       <c r="B25" t="n">
-        <v>129140402460</v>
+        <v>134007926327</v>
       </c>
       <c r="C25" t="n">
-        <v>622.4</v>
+        <v>578.1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6478</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>209850046</v>
+        <v>232858811</v>
       </c>
       <c r="B26" t="n">
-        <v>129511468430</v>
+        <v>134153181852</v>
       </c>
       <c r="C26" t="n">
-        <v>617.2</v>
+        <v>576.1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6496</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>210249112</v>
+        <v>238623168</v>
       </c>
       <c r="B27" t="n">
-        <v>129559435691</v>
+        <v>135281028318</v>
       </c>
       <c r="C27" t="n">
-        <v>616.2</v>
+        <v>566.9</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6499</v>
+        <v>0.6785</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>210696050</v>
+        <v>239865014</v>
       </c>
       <c r="B28" t="n">
-        <v>129617422402</v>
+        <v>135496819313</v>
       </c>
       <c r="C28" t="n">
-        <v>615.2</v>
+        <v>564.9</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6502</v>
+        <v>0.6796</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>211766189</v>
+        <v>240815565</v>
       </c>
       <c r="B29" t="n">
-        <v>129762677928</v>
+        <v>135622871714</v>
       </c>
       <c r="C29" t="n">
-        <v>612.8</v>
+        <v>563.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6509</v>
+        <v>0.6802</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>214390533</v>
+        <v>241382091</v>
       </c>
       <c r="B30" t="n">
-        <v>130399782403</v>
+        <v>135700061549</v>
       </c>
       <c r="C30" t="n">
-        <v>608.2</v>
+        <v>562.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6542</v>
+        <v>0.6806</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>214867542</v>
+        <v>242013296</v>
       </c>
       <c r="B31" t="n">
-        <v>130921663758</v>
+        <v>135784250730</v>
       </c>
       <c r="C31" t="n">
-        <v>609.3</v>
+        <v>561.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6567</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>217227399</v>
+        <v>250890874</v>
       </c>
       <c r="B32" t="n">
-        <v>131292729728</v>
+        <v>136716561008</v>
       </c>
       <c r="C32" t="n">
-        <v>604.4</v>
+        <v>544.9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6586</v>
+        <v>0.6857</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>217626465</v>
+        <v>253580283</v>
       </c>
       <c r="B33" t="n">
-        <v>131340696989</v>
+        <v>138106061939</v>
       </c>
       <c r="C33" t="n">
-        <v>603.5</v>
+        <v>544.6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6927</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>218073403</v>
+        <v>254530834</v>
       </c>
       <c r="B34" t="n">
-        <v>131398683700</v>
+        <v>138232114340</v>
       </c>
       <c r="C34" t="n">
-        <v>602.5</v>
+        <v>543.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6591</v>
+        <v>0.6933</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>219143542</v>
+        <v>255097360</v>
       </c>
       <c r="B35" t="n">
-        <v>131543939226</v>
+        <v>138309304176</v>
       </c>
       <c r="C35" t="n">
-        <v>600.3</v>
+        <v>542.2</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6937</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>225163814</v>
+        <v>255728565</v>
       </c>
       <c r="B36" t="n">
-        <v>132003682349</v>
+        <v>138393493356</v>
       </c>
       <c r="C36" t="n">
-        <v>586.3</v>
+        <v>541.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.662</v>
+        <v>0.6942</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>226114365</v>
+        <v>265676206</v>
       </c>
       <c r="B37" t="n">
-        <v>132129734750</v>
+        <v>138986215847</v>
       </c>
       <c r="C37" t="n">
-        <v>584.3</v>
+        <v>523.1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6627</v>
+        <v>0.6971000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>226680891</v>
+        <v>267741841</v>
       </c>
       <c r="B38" t="n">
-        <v>132206924585</v>
+        <v>139246417412</v>
       </c>
       <c r="C38" t="n">
-        <v>583.2</v>
+        <v>520.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6631</v>
+        <v>0.6984</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>227312096</v>
+        <v>272325298</v>
       </c>
       <c r="B39" t="n">
-        <v>132291113766</v>
+        <v>140073497565</v>
       </c>
       <c r="C39" t="n">
-        <v>582</v>
+        <v>514.4</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6635</v>
+        <v>0.7026</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>228582811</v>
+        <v>279391475</v>
       </c>
       <c r="B40" t="n">
-        <v>133530906385</v>
+        <v>141595458473</v>
       </c>
       <c r="C40" t="n">
-        <v>584.2</v>
+        <v>506.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6698</v>
+        <v>0.7102000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>230942668</v>
+        <v>281457110</v>
       </c>
       <c r="B41" t="n">
-        <v>133901972355</v>
+        <v>141855660039</v>
       </c>
       <c r="C41" t="n">
-        <v>579.8</v>
+        <v>504</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6717</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>231341734</v>
+        <v>286427210</v>
       </c>
       <c r="B42" t="n">
-        <v>133949939616</v>
+        <v>143161163745</v>
       </c>
       <c r="C42" t="n">
-        <v>579</v>
+        <v>499.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.7181999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>231788672</v>
+        <v>295931504</v>
       </c>
       <c r="B43" t="n">
-        <v>134007926327</v>
+        <v>145022313898</v>
       </c>
       <c r="C43" t="n">
-        <v>578.1</v>
+        <v>490.1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6722</v>
+        <v>0.7276</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>232858811</v>
+        <v>302640962</v>
       </c>
       <c r="B44" t="n">
-        <v>134153181852</v>
+        <v>145730834459</v>
       </c>
       <c r="C44" t="n">
-        <v>576.1</v>
+        <v>481.5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.7311</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>238623168</v>
+        <v>332373815</v>
       </c>
       <c r="B45" t="n">
-        <v>135281028318</v>
+        <v>145971911604</v>
       </c>
       <c r="C45" t="n">
-        <v>566.9</v>
+        <v>439.2</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6785</v>
+        <v>0.7322</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>239865014</v>
+        <v>332772881</v>
       </c>
       <c r="B46" t="n">
-        <v>135496819313</v>
+        <v>146019878865</v>
       </c>
       <c r="C46" t="n">
-        <v>564.9</v>
+        <v>438.8</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6796</v>
+        <v>0.7324000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>240815565</v>
+        <v>333219819</v>
       </c>
       <c r="B47" t="n">
-        <v>135622871714</v>
+        <v>146077865576</v>
       </c>
       <c r="C47" t="n">
-        <v>563.2</v>
+        <v>438.4</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6802</v>
+        <v>0.7327</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>241382091</v>
+        <v>334289958</v>
       </c>
       <c r="B48" t="n">
-        <v>135700061549</v>
+        <v>146223121101</v>
       </c>
       <c r="C48" t="n">
-        <v>562.2</v>
+        <v>437.4</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6806</v>
+        <v>0.7334000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>242013296</v>
+        <v>339492303</v>
       </c>
       <c r="B49" t="n">
-        <v>135784250730</v>
+        <v>152876568920</v>
       </c>
       <c r="C49" t="n">
-        <v>561.1</v>
+        <v>450.3</v>
       </c>
       <c r="D49" t="n">
-        <v>0.681</v>
+        <v>0.7669</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>252338437</v>
+        <v>342625080</v>
       </c>
       <c r="B50" t="n">
-        <v>137890270945</v>
+        <v>153244145680</v>
       </c>
       <c r="C50" t="n">
-        <v>546.4</v>
+        <v>447.3</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6916</v>
+        <v>0.7687</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>253580283</v>
+        <v>343470682</v>
       </c>
       <c r="B51" t="n">
-        <v>138106061939</v>
+        <v>153476936338</v>
       </c>
       <c r="C51" t="n">
-        <v>544.6</v>
+        <v>446.8</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6927</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254530834</v>
+        <v>344120823</v>
       </c>
       <c r="B52" t="n">
-        <v>138232114340</v>
+        <v>153563651194</v>
       </c>
       <c r="C52" t="n">
-        <v>543.1</v>
+        <v>446.2</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6933</v>
+        <v>0.7703</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>255097360</v>
+        <v>344833424</v>
       </c>
       <c r="B53" t="n">
-        <v>138309304176</v>
+        <v>153654297572</v>
       </c>
       <c r="C53" t="n">
-        <v>542.2</v>
+        <v>445.6</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6937</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>255728565</v>
+        <v>346879746</v>
       </c>
       <c r="B54" t="n">
-        <v>138393493356</v>
+        <v>153982684425</v>
       </c>
       <c r="C54" t="n">
-        <v>541.2</v>
+        <v>443.9</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6942</v>
+        <v>0.7724</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>265676206</v>
+        <v>348996597</v>
       </c>
       <c r="B55" t="n">
-        <v>138986215847</v>
+        <v>154737719073</v>
       </c>
       <c r="C55" t="n">
-        <v>523.1</v>
+        <v>443.4</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.7763</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>267741841</v>
+        <v>350866195</v>
       </c>
       <c r="B56" t="n">
-        <v>139246417412</v>
+        <v>155005768116</v>
       </c>
       <c r="C56" t="n">
-        <v>520.1</v>
+        <v>441.8</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6984</v>
+        <v>0.7776</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>272325298</v>
+        <v>352974977</v>
       </c>
       <c r="B57" t="n">
-        <v>140073497565</v>
+        <v>155338086491</v>
       </c>
       <c r="C57" t="n">
-        <v>514.4</v>
+        <v>440.1</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7026</v>
+        <v>0.7793</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>276146882</v>
+        <v>353625118</v>
       </c>
       <c r="B58" t="n">
-        <v>140161332548</v>
+        <v>155424801347</v>
       </c>
       <c r="C58" t="n">
-        <v>507.6</v>
+        <v>439.5</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7032</v>
+        <v>0.7796999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>279391475</v>
+        <v>354337719</v>
       </c>
       <c r="B59" t="n">
-        <v>141595458473</v>
+        <v>155515447725</v>
       </c>
       <c r="C59" t="n">
-        <v>506.8</v>
+        <v>438.9</v>
       </c>
       <c r="D59" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7801</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>281457110</v>
+        <v>359009847</v>
       </c>
       <c r="B60" t="n">
-        <v>141855660039</v>
+        <v>156163888494</v>
       </c>
       <c r="C60" t="n">
-        <v>504</v>
+        <v>435</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7115</v>
+        <v>0.7834</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>286427210</v>
+        <v>361047177</v>
       </c>
       <c r="B61" t="n">
-        <v>143161163745</v>
+        <v>156223968287</v>
       </c>
       <c r="C61" t="n">
-        <v>499.8</v>
+        <v>432.7</v>
       </c>
       <c r="D61" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7837</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>302359849</v>
+        <v>365719304</v>
       </c>
       <c r="B62" t="n">
-        <v>143513457556</v>
+        <v>156872409056</v>
       </c>
       <c r="C62" t="n">
-        <v>474.6</v>
+        <v>428.9</v>
       </c>
       <c r="D62" t="n">
-        <v>0.7198</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>304376188</v>
+        <v>375493460</v>
       </c>
       <c r="B63" t="n">
-        <v>143844484595</v>
+        <v>157617482870</v>
       </c>
       <c r="C63" t="n">
-        <v>472.6</v>
+        <v>419.8</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7214</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>305118772</v>
+        <v>382202917</v>
       </c>
       <c r="B64" t="n">
-        <v>143932490787</v>
+        <v>158326003432</v>
       </c>
       <c r="C64" t="n">
-        <v>471.7</v>
+        <v>414.2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7219</v>
+        <v>0.7943</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>305897790</v>
+        <v>395636058</v>
       </c>
       <c r="B65" t="n">
-        <v>144016679968</v>
+        <v>158528673077</v>
       </c>
       <c r="C65" t="n">
-        <v>470.8</v>
+        <v>400.7</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7953</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>315544943</v>
+        <v>420265188</v>
       </c>
       <c r="B66" t="n">
-        <v>144255685475</v>
+        <v>158611672663</v>
       </c>
       <c r="C66" t="n">
-        <v>457.2</v>
+        <v>377.4</v>
       </c>
       <c r="D66" t="n">
-        <v>0.7236</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>322346710</v>
+        <v>421153351</v>
       </c>
       <c r="B67" t="n">
-        <v>145696684177</v>
+        <v>165503331831</v>
       </c>
       <c r="C67" t="n">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7307</v>
+        <v>0.8300999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>326141031</v>
+        <v>430657646</v>
       </c>
       <c r="B68" t="n">
-        <v>147950206842</v>
+        <v>167364481984</v>
       </c>
       <c r="C68" t="n">
-        <v>453.6</v>
+        <v>388.6</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7422</v>
+        <v>0.8395</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>329211975</v>
+        <v>437367103</v>
       </c>
       <c r="B69" t="n">
-        <v>149876737723</v>
+        <v>168073002546</v>
       </c>
       <c r="C69" t="n">
-        <v>455.3</v>
+        <v>384.3</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7518</v>
+        <v>0.8431</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>332344752</v>
+        <v>451977344</v>
       </c>
       <c r="B70" t="n">
-        <v>150244314483</v>
+        <v>169821769941</v>
       </c>
       <c r="C70" t="n">
-        <v>452.1</v>
+        <v>375.7</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7537</v>
+        <v>0.8518</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>333190355</v>
+        <v>458686802</v>
       </c>
       <c r="B71" t="n">
-        <v>150477105141</v>
+        <v>170530290502</v>
       </c>
       <c r="C71" t="n">
-        <v>451.6</v>
+        <v>371.8</v>
       </c>
       <c r="D71" t="n">
-        <v>0.7548</v>
+        <v>0.8554</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>333840496</v>
+        <v>473845686</v>
       </c>
       <c r="B72" t="n">
-        <v>150563819997</v>
+        <v>172014451463</v>
       </c>
       <c r="C72" t="n">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="D72" t="n">
-        <v>0.7553</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>334553097</v>
+        <v>480555144</v>
       </c>
       <c r="B73" t="n">
-        <v>150654466375</v>
+        <v>172722972025</v>
       </c>
       <c r="C73" t="n">
-        <v>450.3</v>
+        <v>359.4</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7557</v>
+        <v>0.8663999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>336599419</v>
+        <v>493988285</v>
       </c>
       <c r="B74" t="n">
-        <v>150982853228</v>
+        <v>172925641671</v>
       </c>
       <c r="C74" t="n">
-        <v>448.6</v>
+        <v>350.1</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7574</v>
+        <v>0.8673999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>339225225</v>
+        <v>515301223</v>
       </c>
       <c r="B75" t="n">
-        <v>151302907144</v>
+        <v>175259767784</v>
       </c>
       <c r="C75" t="n">
-        <v>446</v>
+        <v>340.1</v>
       </c>
       <c r="D75" t="n">
-        <v>0.759</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>339492303</v>
+        <v>526091925</v>
       </c>
       <c r="B76" t="n">
-        <v>152876568920</v>
+        <v>175342675766</v>
       </c>
       <c r="C76" t="n">
-        <v>450.3</v>
+        <v>333.3</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7669</v>
+        <v>0.8794999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>342625080</v>
+        <v>533638045</v>
       </c>
       <c r="B77" t="n">
-        <v>153244145680</v>
+        <v>176699130431</v>
       </c>
       <c r="C77" t="n">
-        <v>447.3</v>
+        <v>331.1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.7687</v>
+        <v>0.8863</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>343470682</v>
+        <v>535468155</v>
       </c>
       <c r="B78" t="n">
-        <v>153476936338</v>
+        <v>176884154112</v>
       </c>
       <c r="C78" t="n">
-        <v>446.8</v>
+        <v>330.3</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7699</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>344120823</v>
+        <v>538399755</v>
       </c>
       <c r="B79" t="n">
-        <v>153563651194</v>
+        <v>177159691119</v>
       </c>
       <c r="C79" t="n">
-        <v>446.2</v>
+        <v>329</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7703</v>
+        <v>0.8885999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>344833424</v>
+        <v>540748023</v>
       </c>
       <c r="B80" t="n">
-        <v>153654297572</v>
+        <v>177208551413</v>
       </c>
       <c r="C80" t="n">
-        <v>445.6</v>
+        <v>327.7</v>
       </c>
       <c r="D80" t="n">
-        <v>0.7708</v>
+        <v>0.8889</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>346879746</v>
+        <v>541305980</v>
       </c>
       <c r="B81" t="n">
-        <v>153982684425</v>
+        <v>177385057500</v>
       </c>
       <c r="C81" t="n">
-        <v>443.9</v>
+        <v>327.7</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7724</v>
+        <v>0.8898</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>349505552</v>
+        <v>546320066</v>
       </c>
       <c r="B82" t="n">
-        <v>154302738341</v>
+        <v>177895029971</v>
       </c>
       <c r="C82" t="n">
-        <v>441.5</v>
+        <v>325.6</v>
       </c>
       <c r="D82" t="n">
-        <v>0.774</v>
+        <v>0.8922</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>350866195</v>
+        <v>553602342</v>
       </c>
       <c r="B83" t="n">
-        <v>155005768116</v>
+        <v>178195451613</v>
       </c>
       <c r="C83" t="n">
-        <v>441.8</v>
+        <v>321.9</v>
       </c>
       <c r="D83" t="n">
-        <v>0.7776</v>
+        <v>0.8938</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>353625118</v>
+        <v>555824361</v>
       </c>
       <c r="B84" t="n">
-        <v>155424801347</v>
+        <v>179756180124</v>
       </c>
       <c r="C84" t="n">
-        <v>439.5</v>
+        <v>323.4</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>360334576</v>
+        <v>562533818</v>
       </c>
       <c r="B85" t="n">
-        <v>156133321909</v>
+        <v>180464700686</v>
       </c>
       <c r="C85" t="n">
-        <v>433.3</v>
+        <v>320.8</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7833</v>
+        <v>0.9051</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>395636058</v>
+        <v>579957921</v>
       </c>
       <c r="B86" t="n">
-        <v>158528673077</v>
+        <v>180634228726</v>
       </c>
       <c r="C86" t="n">
-        <v>400.7</v>
+        <v>311.5</v>
       </c>
       <c r="D86" t="n">
-        <v>0.7953</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>410873024</v>
+        <v>584560299</v>
       </c>
       <c r="B87" t="n">
-        <v>162503500634</v>
+        <v>180911439302</v>
       </c>
       <c r="C87" t="n">
-        <v>395.5</v>
+        <v>309.5</v>
       </c>
       <c r="D87" t="n">
-        <v>0.8151</v>
+        <v>0.9075</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>421153351</v>
+        <v>585227554</v>
       </c>
       <c r="B88" t="n">
-        <v>165503331831</v>
+        <v>181160837155</v>
       </c>
       <c r="C88" t="n">
-        <v>393</v>
+        <v>309.6</v>
       </c>
       <c r="D88" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.9087</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>441697017</v>
+        <v>586056043</v>
       </c>
       <c r="B89" t="n">
-        <v>166821938743</v>
+        <v>181230944816</v>
       </c>
       <c r="C89" t="n">
-        <v>377.7</v>
+        <v>309.2</v>
       </c>
       <c r="D89" t="n">
-        <v>0.8367</v>
+        <v>0.9091</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>442473050</v>
+        <v>586877069</v>
       </c>
       <c r="B90" t="n">
-        <v>167960619788</v>
+        <v>181290671128</v>
       </c>
       <c r="C90" t="n">
-        <v>379.6</v>
+        <v>308.9</v>
       </c>
       <c r="D90" t="n">
-        <v>0.8424</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>451977344</v>
+        <v>588814966</v>
       </c>
       <c r="B91" t="n">
-        <v>169821769941</v>
+        <v>181649978047</v>
       </c>
       <c r="C91" t="n">
-        <v>375.7</v>
+        <v>308.5</v>
       </c>
       <c r="D91" t="n">
-        <v>0.8518</v>
+        <v>0.9112</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>458686802</v>
+        <v>589462215</v>
       </c>
       <c r="B92" t="n">
-        <v>170530290502</v>
+        <v>182495378879</v>
       </c>
       <c r="C92" t="n">
-        <v>371.8</v>
+        <v>309.6</v>
       </c>
       <c r="D92" t="n">
-        <v>0.8554</v>
+        <v>0.9155</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>473845686</v>
+        <v>592801414</v>
       </c>
       <c r="B93" t="n">
-        <v>172014451463</v>
+        <v>182673061738</v>
       </c>
       <c r="C93" t="n">
-        <v>363</v>
+        <v>308.2</v>
       </c>
       <c r="D93" t="n">
-        <v>0.8628</v>
+        <v>0.9163</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>480555144</v>
+        <v>594731849</v>
       </c>
       <c r="B94" t="n">
-        <v>172722972025</v>
+        <v>183021987308</v>
       </c>
       <c r="C94" t="n">
-        <v>359.4</v>
+        <v>307.7</v>
       </c>
       <c r="D94" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.9181</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>493988285</v>
+        <v>595560338</v>
       </c>
       <c r="B95" t="n">
-        <v>172925641671</v>
+        <v>183092094969</v>
       </c>
       <c r="C95" t="n">
-        <v>350.1</v>
+        <v>307.4</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.9184</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>518822983</v>
+        <v>596171673</v>
       </c>
       <c r="B96" t="n">
-        <v>173766344447</v>
+        <v>183203899441</v>
       </c>
       <c r="C96" t="n">
-        <v>334.9</v>
+        <v>307.3</v>
       </c>
       <c r="D96" t="n">
-        <v>0.8716</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>526091925</v>
+        <v>601441307</v>
       </c>
       <c r="B97" t="n">
-        <v>175342675766</v>
+        <v>183730507870</v>
       </c>
       <c r="C97" t="n">
-        <v>333.3</v>
+        <v>305.5</v>
       </c>
       <c r="D97" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>533638045</v>
+        <v>602269795</v>
       </c>
       <c r="B98" t="n">
-        <v>176699130431</v>
+        <v>183800615531</v>
       </c>
       <c r="C98" t="n">
-        <v>331.1</v>
+        <v>305.2</v>
       </c>
       <c r="D98" t="n">
-        <v>0.8863</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>538399755</v>
+        <v>603090822</v>
       </c>
       <c r="B99" t="n">
-        <v>177159691119</v>
+        <v>183860341843</v>
       </c>
       <c r="C99" t="n">
-        <v>329</v>
+        <v>304.9</v>
       </c>
       <c r="D99" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.9223</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>546320066</v>
+        <v>608283580</v>
       </c>
       <c r="B100" t="n">
-        <v>177895029971</v>
+        <v>184258602832</v>
       </c>
       <c r="C100" t="n">
-        <v>325.6</v>
+        <v>302.9</v>
       </c>
       <c r="D100" t="n">
-        <v>0.8922</v>
+        <v>0.9243</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>553602342</v>
+        <v>621716721</v>
       </c>
       <c r="B101" t="n">
-        <v>178195451613</v>
+        <v>184461272478</v>
       </c>
       <c r="C101" t="n">
-        <v>321.9</v>
+        <v>296.7</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8938</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>555824361</v>
+        <v>634006164</v>
       </c>
       <c r="B102" t="n">
-        <v>179756180124</v>
+        <v>184748240782</v>
       </c>
       <c r="C102" t="n">
-        <v>323.4</v>
+        <v>291.4</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9016</v>
+        <v>0.9266</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>562533818</v>
+        <v>638770707</v>
       </c>
       <c r="B103" t="n">
-        <v>180464700686</v>
+        <v>184942362628</v>
       </c>
       <c r="C103" t="n">
-        <v>320.8</v>
+        <v>289.5</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9051</v>
+        <v>0.9276</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>573691996</v>
+        <v>639510121</v>
       </c>
       <c r="B104" t="n">
-        <v>180899413446</v>
+        <v>184966958748</v>
       </c>
       <c r="C104" t="n">
-        <v>315.3</v>
+        <v>289.2</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9074</v>
+        <v>0.9277</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>580401453</v>
+        <v>641858390</v>
       </c>
       <c r="B105" t="n">
-        <v>181607934008</v>
+        <v>185015819043</v>
       </c>
       <c r="C105" t="n">
-        <v>312.9</v>
+        <v>288.3</v>
       </c>
       <c r="D105" t="n">
-        <v>0.911</v>
+        <v>0.9278999999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>588814966</v>
+        <v>644768157</v>
       </c>
       <c r="B106" t="n">
-        <v>181649978047</v>
+        <v>185108545563</v>
       </c>
       <c r="C106" t="n">
-        <v>308.5</v>
+        <v>287.1</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9112</v>
+        <v>0.9284</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>589462215</v>
+        <v>647459674</v>
       </c>
       <c r="B107" t="n">
-        <v>182495378879</v>
+        <v>186685528990</v>
       </c>
       <c r="C107" t="n">
-        <v>309.6</v>
+        <v>288.3</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9155</v>
+        <v>0.9364</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>592801414</v>
+        <v>661378463</v>
       </c>
       <c r="B108" t="n">
-        <v>182673061738</v>
+        <v>187159640271</v>
       </c>
       <c r="C108" t="n">
-        <v>308.2</v>
+        <v>283</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9163</v>
+        <v>0.9387</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>594731849</v>
+        <v>668696871</v>
       </c>
       <c r="B109" t="n">
-        <v>183021987308</v>
+        <v>189958074912</v>
       </c>
       <c r="C109" t="n">
-        <v>307.7</v>
+        <v>284.1</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9181</v>
+        <v>0.9528</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>595560338</v>
+        <v>678201166</v>
       </c>
       <c r="B110" t="n">
-        <v>183092094969</v>
+        <v>191819225065</v>
       </c>
       <c r="C110" t="n">
-        <v>307.4</v>
+        <v>282.8</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9184</v>
+        <v>0.9622000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>596171673</v>
+        <v>684910624</v>
       </c>
       <c r="B111" t="n">
-        <v>183203899441</v>
+        <v>192527745627</v>
       </c>
       <c r="C111" t="n">
-        <v>307.3</v>
+        <v>281.1</v>
       </c>
       <c r="D111" t="n">
-        <v>0.919</v>
+        <v>0.9657</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>599510872</v>
+        <v>698343765</v>
       </c>
       <c r="B112" t="n">
-        <v>183381582299</v>
+        <v>192730415273</v>
       </c>
       <c r="C112" t="n">
-        <v>305.9</v>
+        <v>276</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9668</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>601441307</v>
+        <v>764975627</v>
       </c>
       <c r="B113" t="n">
-        <v>183730507870</v>
+        <v>192778167539</v>
       </c>
       <c r="C113" t="n">
-        <v>305.5</v>
+        <v>252</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9217</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>602269795</v>
+        <v>766879363</v>
       </c>
       <c r="B114" t="n">
-        <v>183800615531</v>
+        <v>195667613062</v>
       </c>
       <c r="C114" t="n">
-        <v>305.2</v>
+        <v>255.1</v>
       </c>
       <c r="D114" t="n">
-        <v>0.922</v>
+        <v>0.9814000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>603090822</v>
+        <v>776383657</v>
       </c>
       <c r="B115" t="n">
-        <v>183860341843</v>
+        <v>197528763214</v>
       </c>
       <c r="C115" t="n">
-        <v>304.9</v>
+        <v>254.4</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9223</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>608283580</v>
+        <v>783093115</v>
       </c>
       <c r="B116" t="n">
-        <v>184258602832</v>
+        <v>198237283776</v>
       </c>
       <c r="C116" t="n">
-        <v>302.9</v>
+        <v>253.1</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9243</v>
+        <v>0.9943</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>621716721</v>
+        <v>796263402</v>
       </c>
       <c r="B117" t="n">
-        <v>184461272478</v>
+        <v>199368471000</v>
       </c>
       <c r="C117" t="n">
-        <v>296.7</v>
+        <v>250.4</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9253</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>634006164</v>
+        <v>931963425</v>
       </c>
       <c r="B118" t="n">
-        <v>184748240782</v>
+        <v>200529440906</v>
       </c>
       <c r="C118" t="n">
-        <v>291.4</v>
+        <v>215.2</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9266</v>
+        <v>1.0058</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>638770707</v>
+        <v>938672883</v>
       </c>
       <c r="B119" t="n">
-        <v>184942362628</v>
+        <v>201237961468</v>
       </c>
       <c r="C119" t="n">
-        <v>289.5</v>
+        <v>214.4</v>
       </c>
       <c r="D119" t="n">
-        <v>0.9276</v>
+        <v>1.0094</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>639510121</v>
+        <v>946005586</v>
       </c>
       <c r="B120" t="n">
-        <v>184966958748</v>
+        <v>202355312466</v>
       </c>
       <c r="C120" t="n">
-        <v>289.2</v>
+        <v>213.9</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9277</v>
+        <v>1.015</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>641858390</v>
+        <v>959438727</v>
       </c>
       <c r="B121" t="n">
-        <v>185015819043</v>
+        <v>202557982112</v>
       </c>
       <c r="C121" t="n">
-        <v>288.3</v>
+        <v>211.1</v>
       </c>
       <c r="D121" t="n">
-        <v>0.9278999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>644768157</v>
+        <v>1101585354</v>
       </c>
       <c r="B122" t="n">
-        <v>185108545563</v>
+        <v>205355990158</v>
       </c>
       <c r="C122" t="n">
-        <v>287.1</v>
+        <v>186.4</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9284</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>654669006</v>
+        <v>1115018495</v>
       </c>
       <c r="B123" t="n">
-        <v>186451119709</v>
+        <v>205558659804</v>
       </c>
       <c r="C123" t="n">
-        <v>284.8</v>
+        <v>184.4</v>
       </c>
       <c r="D123" t="n">
-        <v>0.9351</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>661378463</v>
+        <v>1122253479</v>
       </c>
       <c r="B124" t="n">
-        <v>187159640271</v>
+        <v>205874327501</v>
       </c>
       <c r="C124" t="n">
-        <v>283</v>
+        <v>183.4</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9387</v>
+        <v>1.0326</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>668696871</v>
+        <v>1131786994</v>
       </c>
       <c r="B125" t="n">
-        <v>189958074912</v>
+        <v>206006069156</v>
       </c>
       <c r="C125" t="n">
-        <v>284.1</v>
+        <v>182</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9528</v>
+        <v>1.0333</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>678201166</v>
+        <v>1246058321</v>
       </c>
       <c r="B126" t="n">
-        <v>191819225065</v>
+        <v>207714368611</v>
       </c>
       <c r="C126" t="n">
-        <v>282.8</v>
+        <v>166.7</v>
       </c>
       <c r="D126" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.0419</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>684910624</v>
+        <v>1255591836</v>
       </c>
       <c r="B127" t="n">
-        <v>192527745627</v>
+        <v>207846110266</v>
       </c>
       <c r="C127" t="n">
-        <v>281.1</v>
+        <v>165.5</v>
       </c>
       <c r="D127" t="n">
-        <v>0.9657</v>
+        <v>1.0425</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>698343765</v>
+        <v>1390899429</v>
       </c>
       <c r="B128" t="n">
-        <v>192730415273</v>
+        <v>207952304090</v>
       </c>
       <c r="C128" t="n">
-        <v>276</v>
+        <v>149.5</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9668</v>
+        <v>1.043</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>745011021</v>
+        <v>1400432944</v>
       </c>
       <c r="B129" t="n">
-        <v>193474931539</v>
+        <v>208084045745</v>
       </c>
       <c r="C129" t="n">
-        <v>259.7</v>
+        <v>148.6</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9704</v>
+        <v>1.0437</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>754515315</v>
+        <v>1514704271</v>
       </c>
       <c r="B130" t="n">
-        <v>195336081691</v>
+        <v>209792345200</v>
       </c>
       <c r="C130" t="n">
-        <v>258.9</v>
+        <v>138.5</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9798</v>
+        <v>1.0523</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>761224773</v>
+        <v>1524237786</v>
       </c>
       <c r="B131" t="n">
-        <v>196044602253</v>
+        <v>209924086855</v>
       </c>
       <c r="C131" t="n">
-        <v>257.5</v>
+        <v>137.7</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9833</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>776383657</v>
-      </c>
-      <c r="B132" t="n">
-        <v>197528763214</v>
-      </c>
-      <c r="C132" t="n">
-        <v>254.4</v>
-      </c>
-      <c r="D132" t="n">
-        <v>0.9908</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>783093115</v>
-      </c>
-      <c r="B133" t="n">
-        <v>198237283776</v>
-      </c>
-      <c r="C133" t="n">
-        <v>253.1</v>
-      </c>
-      <c r="D133" t="n">
-        <v>0.9943</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>796263402</v>
-      </c>
-      <c r="B134" t="n">
-        <v>199368471000</v>
-      </c>
-      <c r="C134" t="n">
-        <v>250.4</v>
-      </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>929791834</v>
-      </c>
-      <c r="B135" t="n">
-        <v>199785641751</v>
-      </c>
-      <c r="C135" t="n">
-        <v>214.9</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1.0021</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>931963425</v>
-      </c>
-      <c r="B136" t="n">
-        <v>200529440906</v>
-      </c>
-      <c r="C136" t="n">
-        <v>215.2</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1.0058</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>938672883</v>
-      </c>
-      <c r="B137" t="n">
-        <v>201237961468</v>
-      </c>
-      <c r="C137" t="n">
-        <v>214.4</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1.0094</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>939296128</v>
-      </c>
-      <c r="B138" t="n">
-        <v>201646791904</v>
-      </c>
-      <c r="C138" t="n">
-        <v>214.7</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1.0114</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>946005586</v>
-      </c>
-      <c r="B139" t="n">
-        <v>202355312466</v>
-      </c>
-      <c r="C139" t="n">
-        <v>213.9</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1.015</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>959438727</v>
-      </c>
-      <c r="B140" t="n">
-        <v>202557982112</v>
-      </c>
-      <c r="C140" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1.016</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>1085371602</v>
-      </c>
-      <c r="B141" t="n">
-        <v>202786319443</v>
-      </c>
-      <c r="C141" t="n">
-        <v>186.8</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1.0171</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>1094875896</v>
-      </c>
-      <c r="B142" t="n">
-        <v>204647469596</v>
-      </c>
-      <c r="C142" t="n">
-        <v>186.9</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1.0265</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>1101585354</v>
-      </c>
-      <c r="B143" t="n">
-        <v>205355990158</v>
-      </c>
-      <c r="C143" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>1115018495</v>
-      </c>
-      <c r="B144" t="n">
-        <v>205558659804</v>
-      </c>
-      <c r="C144" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1.031</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>1122253479</v>
-      </c>
-      <c r="B145" t="n">
-        <v>205874327501</v>
-      </c>
-      <c r="C145" t="n">
-        <v>183.4</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1.0326</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>1131786994</v>
-      </c>
-      <c r="B146" t="n">
-        <v>206006069156</v>
-      </c>
-      <c r="C146" t="n">
-        <v>182</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1.0333</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>1241296611</v>
-      </c>
-      <c r="B147" t="n">
-        <v>207253807923</v>
-      </c>
-      <c r="C147" t="n">
-        <v>167</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1.0396</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>1246058321</v>
-      </c>
-      <c r="B148" t="n">
-        <v>207714368611</v>
-      </c>
-      <c r="C148" t="n">
-        <v>166.7</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1.0419</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>1255591836</v>
-      </c>
-      <c r="B149" t="n">
-        <v>207846110266</v>
-      </c>
-      <c r="C149" t="n">
-        <v>165.5</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1.0425</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>1390899429</v>
-      </c>
-      <c r="B150" t="n">
-        <v>207952304090</v>
-      </c>
-      <c r="C150" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1.043</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>1400432944</v>
-      </c>
-      <c r="B151" t="n">
-        <v>208084045745</v>
-      </c>
-      <c r="C151" t="n">
-        <v>148.6</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1.0437</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>1509942561</v>
-      </c>
-      <c r="B152" t="n">
-        <v>209331784512</v>
-      </c>
-      <c r="C152" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>1514704271</v>
-      </c>
-      <c r="B153" t="n">
-        <v>209792345200</v>
-      </c>
-      <c r="C153" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1.0523</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>1524237786</v>
-      </c>
-      <c r="B154" t="n">
-        <v>209924086855</v>
-      </c>
-      <c r="C154" t="n">
-        <v>137.7</v>
-      </c>
-      <c r="D154" t="n">
         <v>1.0529</v>
       </c>
     </row>

--- a/results/simulation_workbook.xlsx
+++ b/results/simulation_workbook.xlsx
@@ -10,8 +10,9 @@
     <sheet name="데이터셋요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="케이스비교" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="목표별최적안" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pareto" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pareto차트(PNG)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="예산집행표" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pareto" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pareto차트(PNG)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +35,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,9 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2284,6 +2292,2336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>[안1_매력도우선]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 전체(평균) (회차 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4254667</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.0053</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14445333</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>743.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47645299</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.0594</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E7" t="n">
+        <v>126162393</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1573</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>667.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>256410</v>
+      </c>
+      <c r="E8" t="n">
+        <v>171264957</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.2136</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>557.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>320513</v>
+      </c>
+      <c r="E9" t="n">
+        <v>178643162</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.2228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>350000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>448718</v>
+      </c>
+      <c r="E10" t="n">
+        <v>178230769</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.2223</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>769231</v>
+      </c>
+      <c r="E11" t="n">
+        <v>59794872</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.0746</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E12" t="n">
+        <v>21410256</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.0267</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <f>SUM(B4:B12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="2">
+        <f>SUM(E4:E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 흥행 (회차 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4568000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>384</v>
+      </c>
+      <c r="C18" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15360000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.0176</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>796.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51038462</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.0585</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1049.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E20" t="n">
+        <v>134512821</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.1542</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>722.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>256410</v>
+      </c>
+      <c r="E21" t="n">
+        <v>185196581</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.2123</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>606.6</v>
+      </c>
+      <c r="C22" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>320513</v>
+      </c>
+      <c r="E22" t="n">
+        <v>194423077</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.2229</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>350000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>448718</v>
+      </c>
+      <c r="E23" t="n">
+        <v>195371795</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.2239</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>769231</v>
+      </c>
+      <c r="E24" t="n">
+        <v>67589744</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0.0775</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E25" t="n">
+        <v>24358974</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.0279</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <f>SUM(B17:B25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="2">
+        <f>SUM(E17:E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 비흥행 (회차 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3941333</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13530667</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0.0185</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>690.3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E32" t="n">
+        <v>44252137</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.0605</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E33" t="n">
+        <v>117811966</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.1611</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>613.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>256410</v>
+      </c>
+      <c r="E34" t="n">
+        <v>157333333</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.2151</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>320513</v>
+      </c>
+      <c r="E35" t="n">
+        <v>162863248</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.2227</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>359</v>
+      </c>
+      <c r="C36" t="n">
+        <v>350000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>448718</v>
+      </c>
+      <c r="E36" t="n">
+        <v>161089744</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>769231</v>
+      </c>
+      <c r="E37" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.0711</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E38" t="n">
+        <v>18461538</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0.0252</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B39" s="2">
+        <f>SUM(B30:B38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="2">
+        <f>SUM(E30:E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>[안2_균형]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 전체(평균) (회차 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="C45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4254667</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.0058</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10834000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.0148</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>743.3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D47" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E47" t="n">
+        <v>47645299</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0.0653</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D48" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E48" t="n">
+        <v>126162393</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.1728</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>667.9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D49" t="n">
+        <v>192308</v>
+      </c>
+      <c r="E49" t="n">
+        <v>128448718</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.176</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>557.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D50" t="n">
+        <v>320513</v>
+      </c>
+      <c r="E50" t="n">
+        <v>178643162</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0.2447</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>384615</v>
+      </c>
+      <c r="E51" t="n">
+        <v>152769231</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0.2093</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="C52" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D52" t="n">
+        <v>769231</v>
+      </c>
+      <c r="E52" t="n">
+        <v>59794872</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0.0819</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E53" t="n">
+        <v>21410256</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0.0293</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B54" s="2">
+        <f>SUM(B45:B53)</f>
+        <v/>
+      </c>
+      <c r="E54" s="2">
+        <f>SUM(E45:E53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 흥행 (회차 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D58" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4568000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.0058</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>384</v>
+      </c>
+      <c r="C59" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D59" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>11520000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.0145</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>796.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D60" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E60" t="n">
+        <v>51038462</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.0643</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1049.2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D61" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E61" t="n">
+        <v>134512821</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.1693</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>722.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D62" t="n">
+        <v>192308</v>
+      </c>
+      <c r="E62" t="n">
+        <v>138897436</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0.1749</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>606.6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D63" t="n">
+        <v>320513</v>
+      </c>
+      <c r="E63" t="n">
+        <v>194423077</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>0.2448</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D64" t="n">
+        <v>384615</v>
+      </c>
+      <c r="E64" t="n">
+        <v>167461538</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.2108</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D65" t="n">
+        <v>769231</v>
+      </c>
+      <c r="E65" t="n">
+        <v>67589744</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.0851</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>19</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E66" t="n">
+        <v>24358974</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.0307</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B67" s="2">
+        <f>SUM(B58:B66)</f>
+        <v/>
+      </c>
+      <c r="E67" s="2">
+        <f>SUM(E58:E66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 비흥행 (회차 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D71" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3941333</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.0059</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D72" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10148000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0.0152</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>690.3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D73" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E73" t="n">
+        <v>44252137</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.0665</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="C74" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E74" t="n">
+        <v>117811966</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>613.6</v>
+      </c>
+      <c r="C75" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D75" t="n">
+        <v>192308</v>
+      </c>
+      <c r="E75" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.1773</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D76" t="n">
+        <v>320513</v>
+      </c>
+      <c r="E76" t="n">
+        <v>162863248</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.2447</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>359</v>
+      </c>
+      <c r="C77" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D77" t="n">
+        <v>384615</v>
+      </c>
+      <c r="E77" t="n">
+        <v>138076923</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.2075</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="C78" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D78" t="n">
+        <v>769231</v>
+      </c>
+      <c r="E78" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0.0781</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E79" t="n">
+        <v>18461538</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.0277</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B80" s="2">
+        <f>SUM(B71:B79)</f>
+        <v/>
+      </c>
+      <c r="E80" s="2">
+        <f>SUM(E71:E79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>[안3_효율우선]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 전체(평균) (회차 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="C86" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D86" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4254667</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.0062</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D87" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10834000</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.0157</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>743.3</v>
+      </c>
+      <c r="C88" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D88" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E88" t="n">
+        <v>47645299</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D89" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E89" t="n">
+        <v>126162393</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>667.9</v>
+      </c>
+      <c r="C90" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D90" t="n">
+        <v>192308</v>
+      </c>
+      <c r="E90" t="n">
+        <v>128448718</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.1864</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>557.4</v>
+      </c>
+      <c r="C91" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D91" t="n">
+        <v>256410</v>
+      </c>
+      <c r="E91" t="n">
+        <v>142914530</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.2073</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D92" t="n">
+        <v>384615</v>
+      </c>
+      <c r="E92" t="n">
+        <v>152769231</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.2216</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="C93" t="n">
+        <v>550000</v>
+      </c>
+      <c r="D93" t="n">
+        <v>705128</v>
+      </c>
+      <c r="E93" t="n">
+        <v>54811966</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.0795</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E94" t="n">
+        <v>21410256</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.0311</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B95" s="2">
+        <f>SUM(B86:B94)</f>
+        <v/>
+      </c>
+      <c r="E95" s="2">
+        <f>SUM(E86:E94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 흥행 (회차 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="C99" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D99" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E99" t="n">
+        <v>4568000</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0.0061</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>384</v>
+      </c>
+      <c r="C100" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D100" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E100" t="n">
+        <v>11520000</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.0154</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>796.2</v>
+      </c>
+      <c r="C101" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D101" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E101" t="n">
+        <v>51038462</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1049.2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D102" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E102" t="n">
+        <v>134512821</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0.1794</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>722.3</v>
+      </c>
+      <c r="C103" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D103" t="n">
+        <v>192308</v>
+      </c>
+      <c r="E103" t="n">
+        <v>138897436</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0.1852</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>606.6</v>
+      </c>
+      <c r="C104" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D104" t="n">
+        <v>256410</v>
+      </c>
+      <c r="E104" t="n">
+        <v>155538462</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0.2074</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="C105" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D105" t="n">
+        <v>384615</v>
+      </c>
+      <c r="E105" t="n">
+        <v>167461538</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0.2233</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="C106" t="n">
+        <v>550000</v>
+      </c>
+      <c r="D106" t="n">
+        <v>705128</v>
+      </c>
+      <c r="E106" t="n">
+        <v>61957265</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>19</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E107" t="n">
+        <v>24358974</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.0325</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B108" s="2">
+        <f>SUM(B99:B107)</f>
+        <v/>
+      </c>
+      <c r="E108" s="2">
+        <f>SUM(E99:E107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>시나리오: 비흥행 (회차 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>순입금 구간</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>인원(회차평균)</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>리워드</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>1인예산(제세포함)</t>
+        </is>
+      </c>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>소요예산</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
+          <t>예산비중</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>5,000,000~10,000,000원</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>197.1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D112" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3941333</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0.0063</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10,000,000~15,000,000원</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="C113" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D113" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E113" t="n">
+        <v>10148000</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0.0161</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>15,000,000~30,000,000원</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>690.3</v>
+      </c>
+      <c r="C114" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D114" t="n">
+        <v>64103</v>
+      </c>
+      <c r="E114" t="n">
+        <v>44252137</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0.0704</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>30,000,000~50,000,000원</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="C115" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D115" t="n">
+        <v>128205</v>
+      </c>
+      <c r="E115" t="n">
+        <v>117811966</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0.1874</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>50,000,000~66,000,000원</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>613.6</v>
+      </c>
+      <c r="C116" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D116" t="n">
+        <v>192308</v>
+      </c>
+      <c r="E116" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0.1877</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>66,000,000~90,000,000원</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D117" t="n">
+        <v>256410</v>
+      </c>
+      <c r="E117" t="n">
+        <v>130290598</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.2073</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>90,000,000~130,000,000원</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>359</v>
+      </c>
+      <c r="C118" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D118" t="n">
+        <v>384615</v>
+      </c>
+      <c r="E118" t="n">
+        <v>138076923</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.2196</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>130,000,000~170,000,000원</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="C119" t="n">
+        <v>550000</v>
+      </c>
+      <c r="D119" t="n">
+        <v>705128</v>
+      </c>
+      <c r="E119" t="n">
+        <v>47666667</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>170,000,000원 이상</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1282051</v>
+      </c>
+      <c r="E120" t="n">
+        <v>18461538</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0.0294</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B121" s="2">
+        <f>SUM(B112:B120)</f>
+        <v/>
+      </c>
+      <c r="E121" s="2">
+        <f>SUM(E112:E120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>주: 탄력성 미반영(신청자 유지 가정) 보수적 집계. 모델 추정 예산은 '케이스비교' 시트 참조. 예산 확보는 worst-case 기준 권고.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4141,7 +6479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/results/simulation_workbook.xlsx
+++ b/results/simulation_workbook.xlsx
@@ -191,12 +191,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Pareto'!$A$2:$A$131</f>
+              <f>'Pareto'!$A$2:$A$150</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Pareto'!$B$2:$B$131</f>
+              <f>'Pareto'!$B$2:$B$150</f>
             </numRef>
           </yVal>
         </ser>
@@ -1325,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1343,9 +1343,8 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1416,25 +1415,20 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ROI_%</t>
+          <t>CPA</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CPA</t>
+          <t>평균이전금액</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>평균이전금액</t>
+          <t>수령자당평균리워드</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>수령자당평균리워드</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>매력도지수_배</t>
         </is>
@@ -1483,18 +1477,15 @@
         <v>250.38</v>
       </c>
       <c r="N2" t="n">
-        <v>24938</v>
+        <v>198167</v>
       </c>
       <c r="O2" t="n">
-        <v>198167</v>
+        <v>44412669</v>
       </c>
       <c r="P2" t="n">
-        <v>44412669</v>
+        <v>155940</v>
       </c>
       <c r="Q2" t="n">
-        <v>155940</v>
-      </c>
-      <c r="R2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1541,18 +1532,15 @@
         <v>371.24</v>
       </c>
       <c r="N3" t="n">
-        <v>37024.4</v>
+        <v>130189</v>
       </c>
       <c r="O3" t="n">
-        <v>130189</v>
+        <v>42322939</v>
       </c>
       <c r="P3" t="n">
-        <v>42322939</v>
+        <v>104439</v>
       </c>
       <c r="Q3" t="n">
-        <v>104439</v>
-      </c>
-      <c r="R3" t="n">
         <v>0.8038999999999999</v>
       </c>
     </row>
@@ -1563,55 +1551,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1122253479</v>
+        <v>1131103073</v>
       </c>
       <c r="C4" t="n">
-        <v>102569537</v>
+        <v>103111845</v>
       </c>
       <c r="D4" t="n">
-        <v>1299247163</v>
+        <v>1308397921</v>
       </c>
       <c r="E4" t="n">
-        <v>981712491</v>
+        <v>989846560</v>
       </c>
       <c r="F4" t="n">
-        <v>1220704715</v>
+        <v>1230191374</v>
       </c>
       <c r="G4" t="n">
-        <v>1023802242</v>
+        <v>1032014773</v>
       </c>
       <c r="H4" t="n">
-        <v>205874327501</v>
+        <v>206387814260</v>
       </c>
       <c r="I4" t="n">
-        <v>879533422</v>
+        <v>886436105</v>
       </c>
       <c r="J4" t="n">
-        <v>4596</v>
+        <v>4619</v>
       </c>
       <c r="K4" t="n">
-        <v>4126</v>
+        <v>4148</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5451</v>
+        <v>0.548</v>
       </c>
       <c r="M4" t="n">
-        <v>183.45</v>
+        <v>182.47</v>
       </c>
       <c r="N4" t="n">
-        <v>18244.7</v>
+        <v>272657</v>
       </c>
       <c r="O4" t="n">
-        <v>272021</v>
+        <v>44679335</v>
       </c>
       <c r="P4" t="n">
-        <v>44789582</v>
+        <v>213679</v>
       </c>
       <c r="Q4" t="n">
-        <v>213189</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.0326</v>
+        <v>1.0352</v>
       </c>
     </row>
     <row r="5">
@@ -1621,55 +1606,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>563321326</v>
+        <v>595301294</v>
       </c>
       <c r="C5" t="n">
-        <v>51475946</v>
+        <v>53171953</v>
       </c>
       <c r="D5" t="n">
-        <v>643601478</v>
+        <v>679431026</v>
       </c>
       <c r="E5" t="n">
-        <v>490260673</v>
+        <v>521441493</v>
       </c>
       <c r="F5" t="n">
-        <v>612784325</v>
+        <v>646429972</v>
       </c>
       <c r="G5" t="n">
-        <v>513858327</v>
+        <v>544172616</v>
       </c>
       <c r="H5" t="n">
-        <v>181259295173</v>
+        <v>185872661543</v>
       </c>
       <c r="I5" t="n">
-        <v>443415433</v>
+        <v>468359808</v>
       </c>
       <c r="J5" t="n">
-        <v>4115</v>
+        <v>4224</v>
       </c>
       <c r="K5" t="n">
-        <v>3644</v>
+        <v>3753</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3108</v>
+        <v>0.3203</v>
       </c>
       <c r="M5" t="n">
-        <v>321.77</v>
+        <v>312.23</v>
       </c>
       <c r="N5" t="n">
-        <v>32076.9</v>
+        <v>158634</v>
       </c>
       <c r="O5" t="n">
-        <v>154601</v>
+        <v>44008688</v>
       </c>
       <c r="P5" t="n">
-        <v>44052833</v>
+        <v>124807</v>
       </c>
       <c r="Q5" t="n">
-        <v>121693</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.9091</v>
+        <v>0.9323</v>
       </c>
     </row>
     <row r="6">
@@ -1679,55 +1661,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>442291811</v>
+        <v>461333534</v>
       </c>
       <c r="C6" t="n">
-        <v>39474952</v>
+        <v>41446650</v>
       </c>
       <c r="D6" t="n">
-        <v>504617344</v>
+        <v>526548174</v>
       </c>
       <c r="E6" t="n">
-        <v>387482632</v>
+        <v>403585076</v>
       </c>
       <c r="F6" t="n">
-        <v>480167540</v>
+        <v>501070380</v>
       </c>
       <c r="G6" t="n">
-        <v>404416081</v>
+        <v>421596689</v>
       </c>
       <c r="H6" t="n">
-        <v>168735912960</v>
+        <v>171094499317</v>
       </c>
       <c r="I6" t="n">
-        <v>354433976</v>
+        <v>369286520</v>
       </c>
       <c r="J6" t="n">
-        <v>3862</v>
+        <v>3888</v>
       </c>
       <c r="K6" t="n">
-        <v>3392</v>
+        <v>3417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2621</v>
+        <v>0.2696</v>
       </c>
       <c r="M6" t="n">
-        <v>381.5</v>
+        <v>370.87</v>
       </c>
       <c r="N6" t="n">
-        <v>38050.4</v>
+        <v>135017</v>
       </c>
       <c r="O6" t="n">
-        <v>130409</v>
+        <v>44008931</v>
       </c>
       <c r="P6" t="n">
-        <v>43686312</v>
+        <v>108078</v>
       </c>
       <c r="Q6" t="n">
-        <v>104504</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.8464</v>
+        <v>0.8582</v>
       </c>
     </row>
     <row r="7">
@@ -1737,55 +1716,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>473628533</v>
+        <v>505840544</v>
       </c>
       <c r="C7" t="n">
-        <v>41786622</v>
+        <v>44867349</v>
       </c>
       <c r="D7" t="n">
-        <v>539598122</v>
+        <v>576585652</v>
       </c>
       <c r="E7" t="n">
-        <v>414529654</v>
+        <v>441908399</v>
       </c>
       <c r="F7" t="n">
-        <v>513968420</v>
+        <v>549204331</v>
       </c>
       <c r="G7" t="n">
-        <v>433288646</v>
+        <v>462476757</v>
       </c>
       <c r="H7" t="n">
-        <v>172056148275</v>
+        <v>175545921857</v>
       </c>
       <c r="I7" t="n">
-        <v>374931136</v>
+        <v>400056504</v>
       </c>
       <c r="J7" t="n">
-        <v>4060</v>
+        <v>4128</v>
       </c>
       <c r="K7" t="n">
-        <v>3589</v>
+        <v>3657</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2753</v>
+        <v>0.2882</v>
       </c>
       <c r="M7" t="n">
-        <v>363.27</v>
+        <v>347.04</v>
       </c>
       <c r="N7" t="n">
-        <v>36227.2</v>
+        <v>138305</v>
       </c>
       <c r="O7" t="n">
-        <v>131965</v>
+        <v>42522651</v>
       </c>
       <c r="P7" t="n">
-        <v>42379368</v>
+        <v>109382</v>
       </c>
       <c r="Q7" t="n">
-        <v>104466</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.863</v>
+        <v>0.8804999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1795,55 +1771,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>494640131</v>
+        <v>484540941</v>
       </c>
       <c r="C8" t="n">
-        <v>42625532</v>
+        <v>41914323</v>
       </c>
       <c r="D8" t="n">
-        <v>567780953</v>
+        <v>555919750</v>
       </c>
       <c r="E8" t="n">
-        <v>435071923</v>
+        <v>426238244</v>
       </c>
       <c r="F8" t="n">
-        <v>535758734</v>
+        <v>525155495</v>
       </c>
       <c r="G8" t="n">
-        <v>453521528</v>
+        <v>443926387</v>
       </c>
       <c r="H8" t="n">
-        <v>166630306822</v>
+        <v>164507373239</v>
       </c>
       <c r="I8" t="n">
-        <v>387271948</v>
+        <v>379394579</v>
       </c>
       <c r="J8" t="n">
-        <v>4020</v>
+        <v>3991</v>
       </c>
       <c r="K8" t="n">
-        <v>3549</v>
+        <v>3520</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2968</v>
+        <v>0.2945</v>
       </c>
       <c r="M8" t="n">
-        <v>336.87</v>
+        <v>339.51</v>
       </c>
       <c r="N8" t="n">
-        <v>33587.2</v>
+        <v>137659</v>
       </c>
       <c r="O8" t="n">
-        <v>139383</v>
+        <v>41222388</v>
       </c>
       <c r="P8" t="n">
-        <v>41453985</v>
+        <v>107787</v>
       </c>
       <c r="Q8" t="n">
-        <v>109128</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.8359</v>
+        <v>0.8252</v>
       </c>
     </row>
   </sheetData>
@@ -1857,7 +1830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1875,9 +1848,8 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1948,25 +1920,20 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ROI_%</t>
+          <t>CPA</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CPA</t>
+          <t>평균이전금액</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>평균이전금액</t>
+          <t>수령자당평균리워드</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>수령자당평균리워드</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>매력도지수_배</t>
         </is>
@@ -2015,18 +1982,15 @@
         <v>250.38</v>
       </c>
       <c r="N2" t="n">
-        <v>24938</v>
+        <v>198167</v>
       </c>
       <c r="O2" t="n">
-        <v>198167</v>
+        <v>44412669</v>
       </c>
       <c r="P2" t="n">
-        <v>44412669</v>
+        <v>155940</v>
       </c>
       <c r="Q2" t="n">
-        <v>155940</v>
-      </c>
-      <c r="R2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2037,55 +2001,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>668696871</v>
+        <v>658637696</v>
       </c>
       <c r="C3" t="n">
-        <v>58932404</v>
+        <v>57279206</v>
       </c>
       <c r="D3" t="n">
-        <v>763132342</v>
+        <v>750776902</v>
       </c>
       <c r="E3" t="n">
-        <v>588534469</v>
+        <v>580264441</v>
       </c>
       <c r="F3" t="n">
-        <v>725118944</v>
+        <v>713724255</v>
       </c>
       <c r="G3" t="n">
-        <v>612274799</v>
+        <v>603551137</v>
       </c>
       <c r="H3" t="n">
-        <v>189958074912</v>
+        <v>190012625854</v>
       </c>
       <c r="I3" t="n">
-        <v>523517414</v>
+        <v>517762202</v>
       </c>
       <c r="J3" t="n">
-        <v>4171</v>
+        <v>4347</v>
       </c>
       <c r="K3" t="n">
-        <v>3700</v>
+        <v>3876</v>
       </c>
       <c r="L3" t="n">
-        <v>0.352</v>
+        <v>0.3466</v>
       </c>
       <c r="M3" t="n">
-        <v>284.07</v>
+        <v>288.49</v>
       </c>
       <c r="N3" t="n">
-        <v>28307.2</v>
+        <v>169910</v>
       </c>
       <c r="O3" t="n">
-        <v>180742</v>
+        <v>43708554</v>
       </c>
       <c r="P3" t="n">
-        <v>45546869</v>
+        <v>133568</v>
       </c>
       <c r="Q3" t="n">
-        <v>141501</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.9528</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2095,55 +2056,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>555824361</v>
+        <v>658637696</v>
       </c>
       <c r="C4" t="n">
-        <v>51482969</v>
+        <v>57279206</v>
       </c>
       <c r="D4" t="n">
-        <v>635832580</v>
+        <v>750776902</v>
       </c>
       <c r="E4" t="n">
-        <v>483892311</v>
+        <v>580264441</v>
       </c>
       <c r="F4" t="n">
-        <v>605209607</v>
+        <v>713724255</v>
       </c>
       <c r="G4" t="n">
-        <v>506439114</v>
+        <v>603551137</v>
       </c>
       <c r="H4" t="n">
-        <v>179756180124</v>
+        <v>190012625854</v>
       </c>
       <c r="I4" t="n">
-        <v>443596328</v>
+        <v>517762202</v>
       </c>
       <c r="J4" t="n">
-        <v>4035</v>
+        <v>4347</v>
       </c>
       <c r="K4" t="n">
-        <v>3565</v>
+        <v>3876</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3092</v>
+        <v>0.3466</v>
       </c>
       <c r="M4" t="n">
-        <v>323.4</v>
+        <v>288.49</v>
       </c>
       <c r="N4" t="n">
-        <v>32240.5</v>
+        <v>169910</v>
       </c>
       <c r="O4" t="n">
-        <v>155933</v>
+        <v>43708554</v>
       </c>
       <c r="P4" t="n">
-        <v>44545131</v>
+        <v>133568</v>
       </c>
       <c r="Q4" t="n">
-        <v>124448</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.9016</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2153,55 +2111,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>634006164</v>
+        <v>658637696</v>
       </c>
       <c r="C5" t="n">
-        <v>58809882</v>
+        <v>57279206</v>
       </c>
       <c r="D5" t="n">
-        <v>724252750</v>
+        <v>750776902</v>
       </c>
       <c r="E5" t="n">
-        <v>549837116</v>
+        <v>580264441</v>
       </c>
       <c r="F5" t="n">
-        <v>690126980</v>
+        <v>713724255</v>
       </c>
       <c r="G5" t="n">
-        <v>577885349</v>
+        <v>603551137</v>
       </c>
       <c r="H5" t="n">
-        <v>184748240782</v>
+        <v>190012625854</v>
       </c>
       <c r="I5" t="n">
-        <v>506054215</v>
+        <v>517762202</v>
       </c>
       <c r="J5" t="n">
-        <v>4135</v>
+        <v>4347</v>
       </c>
       <c r="K5" t="n">
-        <v>3664</v>
+        <v>3876</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3432</v>
+        <v>0.3466</v>
       </c>
       <c r="M5" t="n">
-        <v>291.4</v>
+        <v>288.49</v>
       </c>
       <c r="N5" t="n">
-        <v>29039.8</v>
+        <v>169910</v>
       </c>
       <c r="O5" t="n">
-        <v>173029</v>
+        <v>43708554</v>
       </c>
       <c r="P5" t="n">
-        <v>44678946</v>
+        <v>133568</v>
       </c>
       <c r="Q5" t="n">
-        <v>138110</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.9266</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2247,7 +2202,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10000 / 20000 / 50000 / 150000 / 250000 / 450000 / 750000</t>
+          <t>20000 / 30000 / 60000 / 150000 / 230000 / 450000 / 750000</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2217,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20000 / 30000 / 40000 / 100000 / 250000 / 600000 / 1000000</t>
+          <t>20000 / 30000 / 60000 / 150000 / 230000 / 450000 / 750000</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2232,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20000 / 40000 / 40000 / 100000 / 300000 / 550000 / 1000000</t>
+          <t>20000 / 30000 / 60000 / 150000 / 230000 / 450000 / 750000</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2323,7 @@
         <v>4254667</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0053</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="5">
@@ -2390,7 +2345,7 @@
         <v>14445333</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.018</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="6">
@@ -2403,16 +2358,16 @@
         <v>743.3</v>
       </c>
       <c r="C6" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D6" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E6" t="n">
-        <v>47645299</v>
+        <v>57174359</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.0594</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="7">
@@ -2425,16 +2380,16 @@
         <v>984.1</v>
       </c>
       <c r="C7" t="n">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>128205</v>
+        <v>166667</v>
       </c>
       <c r="E7" t="n">
-        <v>126162393</v>
+        <v>164011111</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1573</v>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="8">
@@ -2447,16 +2402,16 @@
         <v>667.9</v>
       </c>
       <c r="C8" t="n">
-        <v>200000</v>
+        <v>140000</v>
       </c>
       <c r="D8" t="n">
-        <v>256410</v>
+        <v>179487</v>
       </c>
       <c r="E8" t="n">
-        <v>171264957</v>
+        <v>119885470</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.2136</v>
+        <v>0.1594</v>
       </c>
     </row>
     <row r="9">
@@ -2469,16 +2424,16 @@
         <v>557.4</v>
       </c>
       <c r="C9" t="n">
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="D9" t="n">
-        <v>320513</v>
+        <v>333333</v>
       </c>
       <c r="E9" t="n">
-        <v>178643162</v>
+        <v>185788889</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.2228</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="10">
@@ -2491,16 +2446,16 @@
         <v>397.2</v>
       </c>
       <c r="C10" t="n">
-        <v>350000</v>
+        <v>270000</v>
       </c>
       <c r="D10" t="n">
-        <v>448718</v>
+        <v>346154</v>
       </c>
       <c r="E10" t="n">
-        <v>178230769</v>
+        <v>137492308</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.2223</v>
+        <v>0.1828</v>
       </c>
     </row>
     <row r="11">
@@ -2513,16 +2468,16 @@
         <v>77.7</v>
       </c>
       <c r="C11" t="n">
-        <v>600000</v>
+        <v>510000</v>
       </c>
       <c r="D11" t="n">
-        <v>769231</v>
+        <v>653846</v>
       </c>
       <c r="E11" t="n">
-        <v>59794872</v>
+        <v>50825641</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.0746</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2535,16 +2490,16 @@
         <v>16.7</v>
       </c>
       <c r="C12" t="n">
-        <v>1000000</v>
+        <v>850000</v>
       </c>
       <c r="D12" t="n">
-        <v>1282051</v>
+        <v>1089744</v>
       </c>
       <c r="E12" t="n">
-        <v>21410256</v>
+        <v>18198718</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.0267</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="13">
@@ -2621,7 +2576,7 @@
         <v>4568000</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="18">
@@ -2643,7 +2598,7 @@
         <v>15360000</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.0176</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="19">
@@ -2656,16 +2611,16 @@
         <v>796.2</v>
       </c>
       <c r="C19" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D19" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E19" t="n">
-        <v>51038462</v>
+        <v>61246154</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.0585</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="20">
@@ -2678,16 +2633,16 @@
         <v>1049.2</v>
       </c>
       <c r="C20" t="n">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="D20" t="n">
-        <v>128205</v>
+        <v>166667</v>
       </c>
       <c r="E20" t="n">
-        <v>134512821</v>
+        <v>174866667</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.1542</v>
+        <v>0.2141</v>
       </c>
     </row>
     <row r="21">
@@ -2700,16 +2655,16 @@
         <v>722.3</v>
       </c>
       <c r="C21" t="n">
-        <v>200000</v>
+        <v>140000</v>
       </c>
       <c r="D21" t="n">
-        <v>256410</v>
+        <v>179487</v>
       </c>
       <c r="E21" t="n">
-        <v>185196581</v>
+        <v>129637607</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.2123</v>
+        <v>0.1587</v>
       </c>
     </row>
     <row r="22">
@@ -2722,16 +2677,16 @@
         <v>606.6</v>
       </c>
       <c r="C22" t="n">
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="D22" t="n">
-        <v>320513</v>
+        <v>333333</v>
       </c>
       <c r="E22" t="n">
-        <v>194423077</v>
+        <v>202200000</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.2229</v>
+        <v>0.2476</v>
       </c>
     </row>
     <row r="23">
@@ -2744,16 +2699,16 @@
         <v>435.4</v>
       </c>
       <c r="C23" t="n">
-        <v>350000</v>
+        <v>270000</v>
       </c>
       <c r="D23" t="n">
-        <v>448718</v>
+        <v>346154</v>
       </c>
       <c r="E23" t="n">
-        <v>195371795</v>
+        <v>150715385</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.2239</v>
+        <v>0.1845</v>
       </c>
     </row>
     <row r="24">
@@ -2766,16 +2721,16 @@
         <v>87.90000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>600000</v>
+        <v>510000</v>
       </c>
       <c r="D24" t="n">
-        <v>769231</v>
+        <v>653846</v>
       </c>
       <c r="E24" t="n">
-        <v>67589744</v>
+        <v>57451282</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.0775</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="25">
@@ -2788,16 +2743,16 @@
         <v>19</v>
       </c>
       <c r="C25" t="n">
-        <v>1000000</v>
+        <v>850000</v>
       </c>
       <c r="D25" t="n">
-        <v>1282051</v>
+        <v>1089744</v>
       </c>
       <c r="E25" t="n">
-        <v>24358974</v>
+        <v>20705128</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.0279</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="26">
@@ -2874,7 +2829,7 @@
         <v>3941333</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="31">
@@ -2896,7 +2851,7 @@
         <v>13530667</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="32">
@@ -2909,16 +2864,16 @@
         <v>690.3</v>
       </c>
       <c r="C32" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D32" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E32" t="n">
-        <v>44252137</v>
+        <v>53102564</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.0605</v>
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2931,16 +2886,16 @@
         <v>918.9</v>
       </c>
       <c r="C33" t="n">
-        <v>100000</v>
+        <v>130000</v>
       </c>
       <c r="D33" t="n">
-        <v>128205</v>
+        <v>166667</v>
       </c>
       <c r="E33" t="n">
-        <v>117811966</v>
+        <v>153155556</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.1611</v>
+        <v>0.2228</v>
       </c>
     </row>
     <row r="34">
@@ -2953,16 +2908,16 @@
         <v>613.6</v>
       </c>
       <c r="C34" t="n">
-        <v>200000</v>
+        <v>140000</v>
       </c>
       <c r="D34" t="n">
-        <v>256410</v>
+        <v>179487</v>
       </c>
       <c r="E34" t="n">
-        <v>157333333</v>
+        <v>110133333</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.2151</v>
+        <v>0.1602</v>
       </c>
     </row>
     <row r="35">
@@ -2975,16 +2930,16 @@
         <v>508.1</v>
       </c>
       <c r="C35" t="n">
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="D35" t="n">
-        <v>320513</v>
+        <v>333333</v>
       </c>
       <c r="E35" t="n">
-        <v>162863248</v>
+        <v>169377778</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.2227</v>
+        <v>0.2464</v>
       </c>
     </row>
     <row r="36">
@@ -2997,16 +2952,16 @@
         <v>359</v>
       </c>
       <c r="C36" t="n">
-        <v>350000</v>
+        <v>270000</v>
       </c>
       <c r="D36" t="n">
-        <v>448718</v>
+        <v>346154</v>
       </c>
       <c r="E36" t="n">
-        <v>161089744</v>
+        <v>124269231</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.2203</v>
+        <v>0.1808</v>
       </c>
     </row>
     <row r="37">
@@ -3019,16 +2974,16 @@
         <v>67.59999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>600000</v>
+        <v>510000</v>
       </c>
       <c r="D37" t="n">
-        <v>769231</v>
+        <v>653846</v>
       </c>
       <c r="E37" t="n">
-        <v>52000000</v>
+        <v>44200000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.0711</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="38">
@@ -3041,16 +2996,16 @@
         <v>14.4</v>
       </c>
       <c r="C38" t="n">
-        <v>1000000</v>
+        <v>850000</v>
       </c>
       <c r="D38" t="n">
-        <v>1282051</v>
+        <v>1089744</v>
       </c>
       <c r="E38" t="n">
-        <v>18461538</v>
+        <v>15692308</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.0252</v>
+        <v>0.0228</v>
       </c>
     </row>
     <row r="39">
@@ -3135,7 +3090,7 @@
         <v>4254667</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.0058</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="46">
@@ -3148,16 +3103,16 @@
         <v>361.1</v>
       </c>
       <c r="C46" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D46" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E46" t="n">
-        <v>10834000</v>
+        <v>14445333</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.0148</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="47">
@@ -3170,16 +3125,16 @@
         <v>743.3</v>
       </c>
       <c r="C47" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D47" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E47" t="n">
-        <v>47645299</v>
+        <v>57174359</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.0653</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="48">
@@ -3192,16 +3147,16 @@
         <v>984.1</v>
       </c>
       <c r="C48" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>128205</v>
+        <v>153846</v>
       </c>
       <c r="E48" t="n">
-        <v>126162393</v>
+        <v>151394872</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1728</v>
+        <v>0.2156</v>
       </c>
     </row>
     <row r="49">
@@ -3214,16 +3169,16 @@
         <v>667.9</v>
       </c>
       <c r="C49" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D49" t="n">
-        <v>192308</v>
+        <v>166667</v>
       </c>
       <c r="E49" t="n">
-        <v>128448718</v>
+        <v>111322222</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.176</v>
+        <v>0.1585</v>
       </c>
     </row>
     <row r="50">
@@ -3236,16 +3191,16 @@
         <v>557.4</v>
       </c>
       <c r="C50" t="n">
-        <v>250000</v>
+        <v>240000</v>
       </c>
       <c r="D50" t="n">
-        <v>320513</v>
+        <v>307692</v>
       </c>
       <c r="E50" t="n">
-        <v>178643162</v>
+        <v>171497436</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.2447</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="51">
@@ -3258,16 +3213,16 @@
         <v>397.2</v>
       </c>
       <c r="C51" t="n">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="D51" t="n">
-        <v>384615</v>
+        <v>320513</v>
       </c>
       <c r="E51" t="n">
-        <v>152769231</v>
+        <v>127307692</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2093</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="52">
@@ -3280,16 +3235,16 @@
         <v>77.7</v>
       </c>
       <c r="C52" t="n">
-        <v>600000</v>
+        <v>480000</v>
       </c>
       <c r="D52" t="n">
-        <v>769231</v>
+        <v>615385</v>
       </c>
       <c r="E52" t="n">
-        <v>59794872</v>
+        <v>47835897</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.0819</v>
+        <v>0.06809999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3302,16 +3257,16 @@
         <v>16.7</v>
       </c>
       <c r="C53" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="D53" t="n">
-        <v>1282051</v>
+        <v>1025641</v>
       </c>
       <c r="E53" t="n">
-        <v>21410256</v>
+        <v>17128205</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.0293</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="54">
@@ -3388,7 +3343,7 @@
         <v>4568000</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.0058</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="59">
@@ -3401,16 +3356,16 @@
         <v>384</v>
       </c>
       <c r="C59" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D59" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E59" t="n">
-        <v>11520000</v>
+        <v>15360000</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.0145</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="60">
@@ -3423,16 +3378,16 @@
         <v>796.2</v>
       </c>
       <c r="C60" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D60" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E60" t="n">
-        <v>51038462</v>
+        <v>61246154</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.0643</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="61">
@@ -3445,16 +3400,16 @@
         <v>1049.2</v>
       </c>
       <c r="C61" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D61" t="n">
-        <v>128205</v>
+        <v>153846</v>
       </c>
       <c r="E61" t="n">
-        <v>134512821</v>
+        <v>161415385</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.1693</v>
+        <v>0.2116</v>
       </c>
     </row>
     <row r="62">
@@ -3467,16 +3422,16 @@
         <v>722.3</v>
       </c>
       <c r="C62" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D62" t="n">
-        <v>192308</v>
+        <v>166667</v>
       </c>
       <c r="E62" t="n">
-        <v>138897436</v>
+        <v>120377778</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.1749</v>
+        <v>0.1578</v>
       </c>
     </row>
     <row r="63">
@@ -3489,16 +3444,16 @@
         <v>606.6</v>
       </c>
       <c r="C63" t="n">
-        <v>250000</v>
+        <v>240000</v>
       </c>
       <c r="D63" t="n">
-        <v>320513</v>
+        <v>307692</v>
       </c>
       <c r="E63" t="n">
-        <v>194423077</v>
+        <v>186646154</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2448</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="64">
@@ -3511,16 +3466,16 @@
         <v>435.4</v>
       </c>
       <c r="C64" t="n">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="D64" t="n">
-        <v>384615</v>
+        <v>320513</v>
       </c>
       <c r="E64" t="n">
-        <v>167461538</v>
+        <v>139551282</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2108</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="65">
@@ -3533,16 +3488,16 @@
         <v>87.90000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>600000</v>
+        <v>480000</v>
       </c>
       <c r="D65" t="n">
-        <v>769231</v>
+        <v>615385</v>
       </c>
       <c r="E65" t="n">
-        <v>67589744</v>
+        <v>54071795</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.0851</v>
+        <v>0.0709</v>
       </c>
     </row>
     <row r="66">
@@ -3555,16 +3510,16 @@
         <v>19</v>
       </c>
       <c r="C66" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="D66" t="n">
-        <v>1282051</v>
+        <v>1025641</v>
       </c>
       <c r="E66" t="n">
-        <v>24358974</v>
+        <v>19487179</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.0307</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="67">
@@ -3641,7 +3596,7 @@
         <v>3941333</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="72">
@@ -3654,16 +3609,16 @@
         <v>338.3</v>
       </c>
       <c r="C72" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D72" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E72" t="n">
-        <v>10148000</v>
+        <v>13530667</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.0152</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="73">
@@ -3676,16 +3631,16 @@
         <v>690.3</v>
       </c>
       <c r="C73" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D73" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E73" t="n">
-        <v>44252137</v>
+        <v>53102564</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.0665</v>
+        <v>0.0827</v>
       </c>
     </row>
     <row r="74">
@@ -3698,16 +3653,16 @@
         <v>918.9</v>
       </c>
       <c r="C74" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D74" t="n">
-        <v>128205</v>
+        <v>153846</v>
       </c>
       <c r="E74" t="n">
-        <v>117811966</v>
+        <v>141374359</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.177</v>
+        <v>0.2202</v>
       </c>
     </row>
     <row r="75">
@@ -3720,16 +3675,16 @@
         <v>613.6</v>
       </c>
       <c r="C75" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D75" t="n">
-        <v>192308</v>
+        <v>166667</v>
       </c>
       <c r="E75" t="n">
-        <v>118000000</v>
+        <v>102266667</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1773</v>
+        <v>0.1593</v>
       </c>
     </row>
     <row r="76">
@@ -3742,16 +3697,16 @@
         <v>508.1</v>
       </c>
       <c r="C76" t="n">
-        <v>250000</v>
+        <v>240000</v>
       </c>
       <c r="D76" t="n">
-        <v>320513</v>
+        <v>307692</v>
       </c>
       <c r="E76" t="n">
-        <v>162863248</v>
+        <v>156348718</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2447</v>
+        <v>0.2435</v>
       </c>
     </row>
     <row r="77">
@@ -3764,16 +3719,16 @@
         <v>359</v>
       </c>
       <c r="C77" t="n">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="D77" t="n">
-        <v>384615</v>
+        <v>320513</v>
       </c>
       <c r="E77" t="n">
-        <v>138076923</v>
+        <v>115064103</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2075</v>
+        <v>0.1792</v>
       </c>
     </row>
     <row r="78">
@@ -3786,16 +3741,16 @@
         <v>67.59999999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>600000</v>
+        <v>480000</v>
       </c>
       <c r="D78" t="n">
-        <v>769231</v>
+        <v>615385</v>
       </c>
       <c r="E78" t="n">
-        <v>52000000</v>
+        <v>41600000</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.0781</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="79">
@@ -3808,16 +3763,16 @@
         <v>14.4</v>
       </c>
       <c r="C79" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="D79" t="n">
-        <v>1282051</v>
+        <v>1025641</v>
       </c>
       <c r="E79" t="n">
-        <v>18461538</v>
+        <v>14769231</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.0277</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="80">
@@ -3924,7 +3879,7 @@
         <v>10834000</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.0157</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="88">
@@ -3937,16 +3892,16 @@
         <v>743.3</v>
       </c>
       <c r="C88" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D88" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E88" t="n">
-        <v>47645299</v>
+        <v>57174359</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0838</v>
       </c>
     </row>
     <row r="89">
@@ -3959,16 +3914,16 @@
         <v>984.1</v>
       </c>
       <c r="C89" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D89" t="n">
-        <v>128205</v>
+        <v>153846</v>
       </c>
       <c r="E89" t="n">
-        <v>126162393</v>
+        <v>151394872</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.183</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="90">
@@ -3981,16 +3936,16 @@
         <v>667.9</v>
       </c>
       <c r="C90" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D90" t="n">
-        <v>192308</v>
+        <v>166667</v>
       </c>
       <c r="E90" t="n">
-        <v>128448718</v>
+        <v>111322222</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.1864</v>
+        <v>0.1631</v>
       </c>
     </row>
     <row r="91">
@@ -4003,16 +3958,16 @@
         <v>557.4</v>
       </c>
       <c r="C91" t="n">
-        <v>200000</v>
+        <v>230000</v>
       </c>
       <c r="D91" t="n">
-        <v>256410</v>
+        <v>294872</v>
       </c>
       <c r="E91" t="n">
-        <v>142914530</v>
+        <v>164351709</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.2073</v>
+        <v>0.2408</v>
       </c>
     </row>
     <row r="92">
@@ -4025,16 +3980,16 @@
         <v>397.2</v>
       </c>
       <c r="C92" t="n">
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="D92" t="n">
-        <v>384615</v>
+        <v>307692</v>
       </c>
       <c r="E92" t="n">
-        <v>152769231</v>
+        <v>122215385</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.2216</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="93">
@@ -4047,16 +4002,16 @@
         <v>77.7</v>
       </c>
       <c r="C93" t="n">
-        <v>550000</v>
+        <v>450000</v>
       </c>
       <c r="D93" t="n">
-        <v>705128</v>
+        <v>576923</v>
       </c>
       <c r="E93" t="n">
-        <v>54811966</v>
+        <v>44846154</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.0795</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -4069,16 +4024,16 @@
         <v>16.7</v>
       </c>
       <c r="C94" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
       <c r="D94" t="n">
-        <v>1282051</v>
+        <v>961538</v>
       </c>
       <c r="E94" t="n">
-        <v>21410256</v>
+        <v>16057692</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.0311</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="95">
@@ -4155,7 +4110,7 @@
         <v>4568000</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.0061</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="100">
@@ -4177,7 +4132,7 @@
         <v>11520000</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.0154</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="101">
@@ -4190,16 +4145,16 @@
         <v>796.2</v>
       </c>
       <c r="C101" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D101" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E101" t="n">
-        <v>51038462</v>
+        <v>61246154</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0827</v>
       </c>
     </row>
     <row r="102">
@@ -4212,16 +4167,16 @@
         <v>1049.2</v>
       </c>
       <c r="C102" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D102" t="n">
-        <v>128205</v>
+        <v>153846</v>
       </c>
       <c r="E102" t="n">
-        <v>134512821</v>
+        <v>161415385</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.1794</v>
+        <v>0.2179</v>
       </c>
     </row>
     <row r="103">
@@ -4234,16 +4189,16 @@
         <v>722.3</v>
       </c>
       <c r="C103" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D103" t="n">
-        <v>192308</v>
+        <v>166667</v>
       </c>
       <c r="E103" t="n">
-        <v>138897436</v>
+        <v>120377778</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.1852</v>
+        <v>0.1625</v>
       </c>
     </row>
     <row r="104">
@@ -4256,16 +4211,16 @@
         <v>606.6</v>
       </c>
       <c r="C104" t="n">
-        <v>200000</v>
+        <v>230000</v>
       </c>
       <c r="D104" t="n">
-        <v>256410</v>
+        <v>294872</v>
       </c>
       <c r="E104" t="n">
-        <v>155538462</v>
+        <v>178869231</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.2074</v>
+        <v>0.2414</v>
       </c>
     </row>
     <row r="105">
@@ -4278,16 +4233,16 @@
         <v>435.4</v>
       </c>
       <c r="C105" t="n">
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="D105" t="n">
-        <v>384615</v>
+        <v>307692</v>
       </c>
       <c r="E105" t="n">
-        <v>167461538</v>
+        <v>133969231</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>0.2233</v>
+        <v>0.1808</v>
       </c>
     </row>
     <row r="106">
@@ -4300,16 +4255,16 @@
         <v>87.90000000000001</v>
       </c>
       <c r="C106" t="n">
-        <v>550000</v>
+        <v>450000</v>
       </c>
       <c r="D106" t="n">
-        <v>705128</v>
+        <v>576923</v>
       </c>
       <c r="E106" t="n">
-        <v>61957265</v>
+        <v>50692308</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="107">
@@ -4322,16 +4277,16 @@
         <v>19</v>
       </c>
       <c r="C107" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
       <c r="D107" t="n">
-        <v>1282051</v>
+        <v>961538</v>
       </c>
       <c r="E107" t="n">
-        <v>24358974</v>
+        <v>18269231</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.0325</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="108">
@@ -4430,7 +4385,7 @@
         <v>10148000</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.0161</v>
+        <v>0.0163</v>
       </c>
     </row>
     <row r="114">
@@ -4443,16 +4398,16 @@
         <v>690.3</v>
       </c>
       <c r="C114" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D114" t="n">
-        <v>64103</v>
+        <v>76923</v>
       </c>
       <c r="E114" t="n">
-        <v>44252137</v>
+        <v>53102564</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.0704</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="115">
@@ -4465,16 +4420,16 @@
         <v>918.9</v>
       </c>
       <c r="C115" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D115" t="n">
-        <v>128205</v>
+        <v>153846</v>
       </c>
       <c r="E115" t="n">
-        <v>117811966</v>
+        <v>141374359</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0.1874</v>
+        <v>0.2266</v>
       </c>
     </row>
     <row r="116">
@@ -4487,16 +4442,16 @@
         <v>613.6</v>
       </c>
       <c r="C116" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D116" t="n">
-        <v>192308</v>
+        <v>166667</v>
       </c>
       <c r="E116" t="n">
-        <v>118000000</v>
+        <v>102266667</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0.1877</v>
+        <v>0.1639</v>
       </c>
     </row>
     <row r="117">
@@ -4509,16 +4464,16 @@
         <v>508.1</v>
       </c>
       <c r="C117" t="n">
-        <v>200000</v>
+        <v>230000</v>
       </c>
       <c r="D117" t="n">
-        <v>256410</v>
+        <v>294872</v>
       </c>
       <c r="E117" t="n">
-        <v>130290598</v>
+        <v>149834188</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>0.2073</v>
+        <v>0.2401</v>
       </c>
     </row>
     <row r="118">
@@ -4531,16 +4486,16 @@
         <v>359</v>
       </c>
       <c r="C118" t="n">
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="D118" t="n">
-        <v>384615</v>
+        <v>307692</v>
       </c>
       <c r="E118" t="n">
-        <v>138076923</v>
+        <v>110461538</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.2196</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="119">
@@ -4553,16 +4508,16 @@
         <v>67.59999999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>550000</v>
+        <v>450000</v>
       </c>
       <c r="D119" t="n">
-        <v>705128</v>
+        <v>576923</v>
       </c>
       <c r="E119" t="n">
-        <v>47666667</v>
+        <v>39000000</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="120">
@@ -4575,16 +4530,16 @@
         <v>14.4</v>
       </c>
       <c r="C120" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
       <c r="D120" t="n">
-        <v>1282051</v>
+        <v>961538</v>
       </c>
       <c r="E120" t="n">
-        <v>18461538</v>
+        <v>13846154</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.0222</v>
       </c>
     </row>
     <row r="121">
@@ -4622,7 +4577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4655,1822 +4610,2088 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126809087</v>
+        <v>145412414</v>
       </c>
       <c r="B2" t="n">
-        <v>113609173389</v>
+        <v>116780233379</v>
       </c>
       <c r="C2" t="n">
-        <v>895.9</v>
+        <v>803.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5698</v>
+        <v>0.5857</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>141510287</v>
+        <v>152671625</v>
       </c>
       <c r="B3" t="n">
-        <v>117102310353</v>
+        <v>117638015754</v>
       </c>
       <c r="C3" t="n">
-        <v>827.5</v>
+        <v>770.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5874</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>155225557</v>
+        <v>156887863</v>
       </c>
       <c r="B4" t="n">
-        <v>119711552979</v>
+        <v>118962888349</v>
       </c>
       <c r="C4" t="n">
-        <v>771.2</v>
+        <v>758.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6005</v>
+        <v>0.5967</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>185974063</v>
+        <v>159252605</v>
       </c>
       <c r="B5" t="n">
-        <v>124297402813</v>
+        <v>119451054416</v>
       </c>
       <c r="C5" t="n">
-        <v>668.4</v>
+        <v>750.1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5991</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>200675263</v>
+        <v>160113614</v>
       </c>
       <c r="B6" t="n">
-        <v>127790539777</v>
+        <v>120273370343</v>
       </c>
       <c r="C6" t="n">
-        <v>636.8</v>
+        <v>751.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.641</v>
+        <v>0.6032999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202526199</v>
+        <v>164837198</v>
       </c>
       <c r="B7" t="n">
-        <v>127799592764</v>
+        <v>120605552842</v>
       </c>
       <c r="C7" t="n">
-        <v>631</v>
+        <v>731.7</v>
       </c>
       <c r="D7" t="n">
-        <v>0.641</v>
+        <v>0.6049</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202925265</v>
+        <v>168125702</v>
       </c>
       <c r="B8" t="n">
-        <v>127847560026</v>
+        <v>121551821228</v>
       </c>
       <c r="C8" t="n">
-        <v>630</v>
+        <v>723</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6412</v>
+        <v>0.6097</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>203372203</v>
+        <v>171589063</v>
       </c>
       <c r="B9" t="n">
-        <v>127905546737</v>
+        <v>122456025313</v>
       </c>
       <c r="C9" t="n">
-        <v>628.9</v>
+        <v>713.7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6415</v>
+        <v>0.6142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>204442342</v>
+        <v>172690626</v>
       </c>
       <c r="B10" t="n">
-        <v>128050802262</v>
+        <v>122844663662</v>
       </c>
       <c r="C10" t="n">
-        <v>626.3</v>
+        <v>711.4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6423</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>205684188</v>
+        <v>175366211</v>
       </c>
       <c r="B11" t="n">
-        <v>128266593257</v>
+        <v>123253318476</v>
       </c>
       <c r="C11" t="n">
-        <v>623.6</v>
+        <v>702.8</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6434</v>
+        <v>0.6182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>214390533</v>
+        <v>175449549</v>
       </c>
       <c r="B12" t="n">
-        <v>130399782403</v>
+        <v>123263696893</v>
       </c>
       <c r="C12" t="n">
-        <v>608.2</v>
+        <v>702.6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6542</v>
+        <v>0.6183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>214867542</v>
+        <v>175534804</v>
       </c>
       <c r="B13" t="n">
-        <v>130921663758</v>
+        <v>123274478381</v>
       </c>
       <c r="C13" t="n">
-        <v>609.3</v>
+        <v>702.3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6567</v>
+        <v>0.6183</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>217227399</v>
+        <v>177797817</v>
       </c>
       <c r="B14" t="n">
-        <v>131292729728</v>
+        <v>123312557188</v>
       </c>
       <c r="C14" t="n">
-        <v>604.4</v>
+        <v>693.6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6586</v>
+        <v>0.6185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>217626465</v>
+        <v>179538398</v>
       </c>
       <c r="B15" t="n">
-        <v>131340696989</v>
+        <v>124098689806</v>
       </c>
       <c r="C15" t="n">
-        <v>603.5</v>
+        <v>691.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>218073403</v>
+        <v>181206236</v>
       </c>
       <c r="B16" t="n">
-        <v>131398683700</v>
+        <v>124663874267</v>
       </c>
       <c r="C16" t="n">
-        <v>602.5</v>
+        <v>688</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6591</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>219143542</v>
+        <v>182826902</v>
       </c>
       <c r="B17" t="n">
-        <v>131543939226</v>
+        <v>125044958192</v>
       </c>
       <c r="C17" t="n">
-        <v>600.3</v>
+        <v>684</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>225163814</v>
+        <v>192256791</v>
       </c>
       <c r="B18" t="n">
-        <v>132003682349</v>
+        <v>126414516170</v>
       </c>
       <c r="C18" t="n">
-        <v>586.3</v>
+        <v>657.5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.662</v>
+        <v>0.6341</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>226114365</v>
+        <v>192681685</v>
       </c>
       <c r="B19" t="n">
-        <v>132129734750</v>
+        <v>126846529238</v>
       </c>
       <c r="C19" t="n">
-        <v>584.3</v>
+        <v>658.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6627</v>
+        <v>0.6363</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>226680891</v>
+        <v>196458833</v>
       </c>
       <c r="B20" t="n">
-        <v>132206924585</v>
+        <v>127643822401</v>
       </c>
       <c r="C20" t="n">
-        <v>583.2</v>
+        <v>649.7</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6631</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>227312096</v>
+        <v>196542171</v>
       </c>
       <c r="B21" t="n">
-        <v>132291113766</v>
+        <v>127654200818</v>
       </c>
       <c r="C21" t="n">
-        <v>582</v>
+        <v>649.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6635</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>229439814</v>
+        <v>196627426</v>
       </c>
       <c r="B22" t="n">
-        <v>132625957817</v>
+        <v>127664982305</v>
       </c>
       <c r="C22" t="n">
-        <v>578</v>
+        <v>649.3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6652</v>
+        <v>0.6404</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>230942668</v>
+        <v>198890439</v>
       </c>
       <c r="B23" t="n">
-        <v>133901972355</v>
+        <v>127703061112</v>
       </c>
       <c r="C23" t="n">
-        <v>579.8</v>
+        <v>642.1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6717</v>
+        <v>0.6405999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>231341734</v>
+        <v>200631021</v>
       </c>
       <c r="B24" t="n">
-        <v>133949939616</v>
+        <v>128489193730</v>
       </c>
       <c r="C24" t="n">
-        <v>579</v>
+        <v>640.4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6445</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>231788672</v>
+        <v>206131980</v>
       </c>
       <c r="B25" t="n">
-        <v>134007926327</v>
+        <v>128674052333</v>
       </c>
       <c r="C25" t="n">
-        <v>578.1</v>
+        <v>624.2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6722</v>
+        <v>0.6454</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>232858811</v>
+        <v>208772402</v>
       </c>
       <c r="B26" t="n">
-        <v>134153181852</v>
+        <v>129077002773</v>
       </c>
       <c r="C26" t="n">
-        <v>576.1</v>
+        <v>618.3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6474</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>238623168</v>
+        <v>208890903</v>
       </c>
       <c r="B27" t="n">
-        <v>135281028318</v>
+        <v>129093085564</v>
       </c>
       <c r="C27" t="n">
-        <v>566.9</v>
+        <v>618</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6785</v>
+        <v>0.6475</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>239865014</v>
+        <v>209012011</v>
       </c>
       <c r="B28" t="n">
-        <v>135496819313</v>
+        <v>129109451856</v>
       </c>
       <c r="C28" t="n">
-        <v>564.9</v>
+        <v>617.7</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6796</v>
+        <v>0.6475</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>240815565</v>
+        <v>211239171</v>
       </c>
       <c r="B29" t="n">
-        <v>135622871714</v>
+        <v>129141945859</v>
       </c>
       <c r="C29" t="n">
-        <v>563.2</v>
+        <v>611.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6802</v>
+        <v>0.6477000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>241382091</v>
+        <v>213349413</v>
       </c>
       <c r="B30" t="n">
-        <v>135700061549</v>
+        <v>130805020095</v>
       </c>
       <c r="C30" t="n">
-        <v>562.2</v>
+        <v>613.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6806</v>
+        <v>0.6561</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>242013296</v>
+        <v>216268256</v>
       </c>
       <c r="B31" t="n">
-        <v>135784250730</v>
+        <v>130874346863</v>
       </c>
       <c r="C31" t="n">
-        <v>561.1</v>
+        <v>605.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.681</v>
+        <v>0.6564</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>250890874</v>
+        <v>217626465</v>
       </c>
       <c r="B32" t="n">
-        <v>136716561008</v>
+        <v>131340696989</v>
       </c>
       <c r="C32" t="n">
-        <v>544.9</v>
+        <v>603.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6857</v>
+        <v>0.6588000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>253580283</v>
+        <v>225118251</v>
       </c>
       <c r="B33" t="n">
-        <v>138106061939</v>
+        <v>132772410392</v>
       </c>
       <c r="C33" t="n">
-        <v>544.6</v>
+        <v>589.8</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6927</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254530834</v>
+        <v>229865024</v>
       </c>
       <c r="B34" t="n">
-        <v>138232114340</v>
+        <v>133467506697</v>
       </c>
       <c r="C34" t="n">
-        <v>543.1</v>
+        <v>580.6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6933</v>
+        <v>0.6694</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>255097360</v>
+        <v>229983526</v>
       </c>
       <c r="B35" t="n">
-        <v>138309304176</v>
+        <v>133483589489</v>
       </c>
       <c r="C35" t="n">
-        <v>542.2</v>
+        <v>580.4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6937</v>
+        <v>0.6695</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>255728565</v>
+        <v>230104633</v>
       </c>
       <c r="B36" t="n">
-        <v>138393493356</v>
+        <v>133499955780</v>
       </c>
       <c r="C36" t="n">
-        <v>541.2</v>
+        <v>580.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6942</v>
+        <v>0.6696</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>265676206</v>
+        <v>231341734</v>
       </c>
       <c r="B37" t="n">
-        <v>138986215847</v>
+        <v>133949939616</v>
       </c>
       <c r="C37" t="n">
-        <v>523.1</v>
+        <v>579</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>267741841</v>
+        <v>234865140</v>
       </c>
       <c r="B38" t="n">
-        <v>139246417412</v>
+        <v>134142615627</v>
       </c>
       <c r="C38" t="n">
-        <v>520.1</v>
+        <v>571.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6984</v>
+        <v>0.6728</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>272325298</v>
+        <v>236368270</v>
       </c>
       <c r="B39" t="n">
-        <v>140073497565</v>
+        <v>134335702711</v>
       </c>
       <c r="C39" t="n">
-        <v>514.4</v>
+        <v>568.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7026</v>
+        <v>0.6738</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>279391475</v>
+        <v>236451608</v>
       </c>
       <c r="B40" t="n">
-        <v>141595458473</v>
+        <v>134346081128</v>
       </c>
       <c r="C40" t="n">
-        <v>506.8</v>
+        <v>568.2</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6739000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>281457110</v>
+        <v>236536863</v>
       </c>
       <c r="B41" t="n">
-        <v>141855660039</v>
+        <v>134356862616</v>
       </c>
       <c r="C41" t="n">
-        <v>504</v>
+        <v>568</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7115</v>
+        <v>0.6739000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>286427210</v>
+        <v>238799876</v>
       </c>
       <c r="B42" t="n">
-        <v>143161163745</v>
+        <v>134394941423</v>
       </c>
       <c r="C42" t="n">
-        <v>499.8</v>
+        <v>562.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.6741</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>295931504</v>
+        <v>240540458</v>
       </c>
       <c r="B43" t="n">
-        <v>145022313898</v>
+        <v>135181074041</v>
       </c>
       <c r="C43" t="n">
-        <v>490.1</v>
+        <v>562</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7276</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>302640962</v>
+        <v>246306392</v>
       </c>
       <c r="B44" t="n">
-        <v>145730834459</v>
+        <v>136147652175</v>
       </c>
       <c r="C44" t="n">
-        <v>481.5</v>
+        <v>552.8</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7311</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>332373815</v>
+        <v>246790767</v>
       </c>
       <c r="B45" t="n">
-        <v>145971911604</v>
+        <v>136634408766</v>
       </c>
       <c r="C45" t="n">
-        <v>439.2</v>
+        <v>553.6</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7322</v>
+        <v>0.6853</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>332772881</v>
+        <v>250083540</v>
       </c>
       <c r="B46" t="n">
-        <v>146019878865</v>
+        <v>136944945337</v>
       </c>
       <c r="C46" t="n">
-        <v>438.8</v>
+        <v>547.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.6869</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>333219819</v>
+        <v>250166878</v>
       </c>
       <c r="B47" t="n">
-        <v>146077865576</v>
+        <v>136955323755</v>
       </c>
       <c r="C47" t="n">
-        <v>438.4</v>
+        <v>547.5</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7327</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>334289958</v>
+        <v>250252133</v>
       </c>
       <c r="B48" t="n">
-        <v>146223121101</v>
+        <v>136966105242</v>
       </c>
       <c r="C48" t="n">
-        <v>437.4</v>
+        <v>547.3</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>339492303</v>
+        <v>251067819</v>
       </c>
       <c r="B49" t="n">
-        <v>152876568920</v>
+        <v>137170085660</v>
       </c>
       <c r="C49" t="n">
-        <v>450.3</v>
+        <v>546.3</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7669</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>342625080</v>
+        <v>254255727</v>
       </c>
       <c r="B50" t="n">
-        <v>153244145680</v>
+        <v>137790316667</v>
       </c>
       <c r="C50" t="n">
-        <v>447.3</v>
+        <v>541.9</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7687</v>
+        <v>0.6912</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>343470682</v>
+        <v>264783089</v>
       </c>
       <c r="B51" t="n">
-        <v>153476936338</v>
+        <v>139779328287</v>
       </c>
       <c r="C51" t="n">
-        <v>446.8</v>
+        <v>527.9</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7699</v>
+        <v>0.7010999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>344120823</v>
+        <v>269774462</v>
       </c>
       <c r="B52" t="n">
-        <v>153563651194</v>
+        <v>140159387008</v>
       </c>
       <c r="C52" t="n">
-        <v>446.2</v>
+        <v>519.5</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7703</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>344833424</v>
+        <v>269892963</v>
       </c>
       <c r="B53" t="n">
-        <v>153654297572</v>
+        <v>140175469799</v>
       </c>
       <c r="C53" t="n">
-        <v>445.6</v>
+        <v>519.4</v>
       </c>
       <c r="D53" t="n">
-        <v>0.7708</v>
+        <v>0.7030999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>346879746</v>
+        <v>270014070</v>
       </c>
       <c r="B54" t="n">
-        <v>153982684425</v>
+        <v>140191836091</v>
       </c>
       <c r="C54" t="n">
-        <v>443.9</v>
+        <v>519.2</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7724</v>
+        <v>0.7030999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>348996597</v>
+        <v>272241231</v>
       </c>
       <c r="B55" t="n">
-        <v>154737719073</v>
+        <v>140224330094</v>
       </c>
       <c r="C55" t="n">
-        <v>443.4</v>
+        <v>515.1</v>
       </c>
       <c r="D55" t="n">
-        <v>0.7763</v>
+        <v>0.7033</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>350866195</v>
+        <v>272583493</v>
       </c>
       <c r="B56" t="n">
-        <v>155005768116</v>
+        <v>140241399830</v>
       </c>
       <c r="C56" t="n">
-        <v>441.8</v>
+        <v>514.5</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7776</v>
+        <v>0.7035</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>352974977</v>
+        <v>274462364</v>
       </c>
       <c r="B57" t="n">
-        <v>155338086491</v>
+        <v>140448707284</v>
       </c>
       <c r="C57" t="n">
-        <v>440.1</v>
+        <v>511.7</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7793</v>
+        <v>0.7045</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>353625118</v>
+        <v>274774577</v>
       </c>
       <c r="B58" t="n">
-        <v>155424801347</v>
+        <v>140834495938</v>
       </c>
       <c r="C58" t="n">
-        <v>439.5</v>
+        <v>512.5</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7064</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>354337719</v>
+        <v>278742958</v>
       </c>
       <c r="B59" t="n">
-        <v>155515447725</v>
+        <v>142073533329</v>
       </c>
       <c r="C59" t="n">
-        <v>438.9</v>
+        <v>509.7</v>
       </c>
       <c r="D59" t="n">
-        <v>0.7801</v>
+        <v>0.7126</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>359009847</v>
+        <v>282087788</v>
       </c>
       <c r="B60" t="n">
-        <v>156163888494</v>
+        <v>142102549983</v>
       </c>
       <c r="C60" t="n">
-        <v>435</v>
+        <v>503.8</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7834</v>
+        <v>0.7128</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>361047177</v>
+        <v>283489731</v>
       </c>
       <c r="B61" t="n">
-        <v>156223968287</v>
+        <v>142768629634</v>
       </c>
       <c r="C61" t="n">
-        <v>432.7</v>
+        <v>503.6</v>
       </c>
       <c r="D61" t="n">
-        <v>0.7837</v>
+        <v>0.7161</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>365719304</v>
+        <v>283608232</v>
       </c>
       <c r="B62" t="n">
-        <v>156872409056</v>
+        <v>142784712426</v>
       </c>
       <c r="C62" t="n">
-        <v>428.9</v>
+        <v>503.5</v>
       </c>
       <c r="D62" t="n">
-        <v>0.787</v>
+        <v>0.7161999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>375493460</v>
+        <v>283729339</v>
       </c>
       <c r="B63" t="n">
-        <v>157617482870</v>
+        <v>142801078717</v>
       </c>
       <c r="C63" t="n">
-        <v>419.8</v>
+        <v>503.3</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7907</v>
+        <v>0.7161999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>382202917</v>
+        <v>285956500</v>
       </c>
       <c r="B64" t="n">
-        <v>158326003432</v>
+        <v>142833572720</v>
       </c>
       <c r="C64" t="n">
-        <v>414.2</v>
+        <v>499.5</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7943</v>
+        <v>0.7164</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>395636058</v>
+        <v>288489847</v>
       </c>
       <c r="B65" t="n">
-        <v>158528673077</v>
+        <v>143443738564</v>
       </c>
       <c r="C65" t="n">
-        <v>400.7</v>
+        <v>497.2</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7953</v>
+        <v>0.7195</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>420265188</v>
+        <v>291452148</v>
       </c>
       <c r="B66" t="n">
-        <v>158611672663</v>
+        <v>144157059043</v>
       </c>
       <c r="C66" t="n">
-        <v>377.4</v>
+        <v>494.6</v>
       </c>
       <c r="D66" t="n">
-        <v>0.7955</v>
+        <v>0.7231</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>421153351</v>
+        <v>294397360</v>
       </c>
       <c r="B67" t="n">
-        <v>165503331831</v>
+        <v>144321237831</v>
       </c>
       <c r="C67" t="n">
-        <v>393</v>
+        <v>490.2</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.7239</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>430657646</v>
+        <v>295252730</v>
       </c>
       <c r="B68" t="n">
-        <v>167364481984</v>
+        <v>144447651132</v>
       </c>
       <c r="C68" t="n">
-        <v>388.6</v>
+        <v>489.2</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8395</v>
+        <v>0.7246</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>437367103</v>
+        <v>295387979</v>
       </c>
       <c r="B69" t="n">
-        <v>168073002546</v>
+        <v>144465426569</v>
       </c>
       <c r="C69" t="n">
-        <v>384.3</v>
+        <v>489.1</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8431</v>
+        <v>0.7247</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>451977344</v>
+        <v>295525747</v>
       </c>
       <c r="B70" t="n">
-        <v>169821769941</v>
+        <v>144483361461</v>
       </c>
       <c r="C70" t="n">
-        <v>375.7</v>
+        <v>488.9</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8518</v>
+        <v>0.7248</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>458686802</v>
+        <v>296164012</v>
       </c>
       <c r="B71" t="n">
-        <v>170530290502</v>
+        <v>145604107614</v>
       </c>
       <c r="C71" t="n">
-        <v>371.8</v>
+        <v>491.6</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8554</v>
+        <v>0.7302999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>473845686</v>
+        <v>299077573</v>
       </c>
       <c r="B72" t="n">
-        <v>172014451463</v>
+        <v>145810901742</v>
       </c>
       <c r="C72" t="n">
-        <v>363</v>
+        <v>487.5</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8628</v>
+        <v>0.7314000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>480555144</v>
+        <v>305668307</v>
       </c>
       <c r="B73" t="n">
-        <v>172722972025</v>
+        <v>147465257767</v>
       </c>
       <c r="C73" t="n">
-        <v>359.4</v>
+        <v>482.4</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.7397</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>493988285</v>
+        <v>311387145</v>
       </c>
       <c r="B74" t="n">
-        <v>172925641671</v>
+        <v>148029589590</v>
       </c>
       <c r="C74" t="n">
-        <v>350.1</v>
+        <v>475.4</v>
       </c>
       <c r="D74" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.7426</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>515301223</v>
+        <v>312242515</v>
       </c>
       <c r="B75" t="n">
-        <v>175259767784</v>
+        <v>148156002890</v>
       </c>
       <c r="C75" t="n">
-        <v>340.1</v>
+        <v>474.5</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8791</v>
+        <v>0.7432</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>526091925</v>
+        <v>312377764</v>
       </c>
       <c r="B76" t="n">
-        <v>175342675766</v>
+        <v>148173778328</v>
       </c>
       <c r="C76" t="n">
-        <v>333.3</v>
+        <v>474.3</v>
       </c>
       <c r="D76" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.7433</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>533638045</v>
+        <v>312515532</v>
       </c>
       <c r="B77" t="n">
-        <v>176699130431</v>
+        <v>148191713220</v>
       </c>
       <c r="C77" t="n">
-        <v>331.1</v>
+        <v>474.2</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8863</v>
+        <v>0.7433999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>535468155</v>
+        <v>313399305</v>
       </c>
       <c r="B78" t="n">
-        <v>176884154112</v>
+        <v>148320128108</v>
       </c>
       <c r="C78" t="n">
-        <v>330.3</v>
+        <v>473.3</v>
       </c>
       <c r="D78" t="n">
-        <v>0.8872</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>538399755</v>
+        <v>318601346</v>
       </c>
       <c r="B79" t="n">
-        <v>177159691119</v>
+        <v>148562148853</v>
       </c>
       <c r="C79" t="n">
-        <v>329</v>
+        <v>466.3</v>
       </c>
       <c r="D79" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>540748023</v>
+        <v>326519518</v>
       </c>
       <c r="B80" t="n">
-        <v>177208551413</v>
+        <v>150607836986</v>
       </c>
       <c r="C80" t="n">
-        <v>327.7</v>
+        <v>461.3</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8889</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>541305980</v>
+        <v>335591131</v>
       </c>
       <c r="B81" t="n">
-        <v>177385057500</v>
+        <v>152270500612</v>
       </c>
       <c r="C81" t="n">
-        <v>327.7</v>
+        <v>453.7</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8898</v>
+        <v>0.7639</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>546320066</v>
+        <v>369500603</v>
       </c>
       <c r="B82" t="n">
-        <v>177895029971</v>
+        <v>156945483759</v>
       </c>
       <c r="C82" t="n">
-        <v>325.6</v>
+        <v>424.8</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8922</v>
+        <v>0.7873</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>553602342</v>
+        <v>379004898</v>
       </c>
       <c r="B83" t="n">
-        <v>178195451613</v>
+        <v>158806633912</v>
       </c>
       <c r="C83" t="n">
-        <v>321.9</v>
+        <v>419</v>
       </c>
       <c r="D83" t="n">
-        <v>0.8938</v>
+        <v>0.7967</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>555824361</v>
+        <v>385714355</v>
       </c>
       <c r="B84" t="n">
-        <v>179756180124</v>
+        <v>159515154474</v>
       </c>
       <c r="C84" t="n">
-        <v>323.4</v>
+        <v>413.6</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9016</v>
+        <v>0.8002</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>562533818</v>
+        <v>417519067</v>
       </c>
       <c r="B85" t="n">
-        <v>180464700686</v>
+        <v>161039971809</v>
       </c>
       <c r="C85" t="n">
-        <v>320.8</v>
+        <v>385.7</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9051</v>
+        <v>0.8076</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>579957921</v>
+        <v>421015838</v>
       </c>
       <c r="B86" t="n">
-        <v>180634228726</v>
+        <v>161910505643</v>
       </c>
       <c r="C86" t="n">
-        <v>311.5</v>
+        <v>384.6</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9061</v>
+        <v>0.8123</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>584560299</v>
+        <v>427023361</v>
       </c>
       <c r="B87" t="n">
-        <v>180911439302</v>
+        <v>162901121962</v>
       </c>
       <c r="C87" t="n">
-        <v>309.5</v>
+        <v>381.5</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9075</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>585227554</v>
+        <v>444013146</v>
       </c>
       <c r="B88" t="n">
-        <v>181160837155</v>
+        <v>166609473721</v>
       </c>
       <c r="C88" t="n">
-        <v>309.6</v>
+        <v>375.2</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9087</v>
+        <v>0.8356</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>586056043</v>
+        <v>479314629</v>
       </c>
       <c r="B89" t="n">
-        <v>181230944816</v>
+        <v>169004824890</v>
       </c>
       <c r="C89" t="n">
-        <v>309.2</v>
+        <v>352.6</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9091</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>586877069</v>
+        <v>481929576</v>
       </c>
       <c r="B90" t="n">
-        <v>181290671128</v>
+        <v>170177891765</v>
       </c>
       <c r="C90" t="n">
-        <v>308.9</v>
+        <v>353.1</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9094</v>
+        <v>0.8535</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>588814966</v>
+        <v>489475697</v>
       </c>
       <c r="B91" t="n">
-        <v>181649978047</v>
+        <v>171534346431</v>
       </c>
       <c r="C91" t="n">
-        <v>308.5</v>
+        <v>350.4</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9112</v>
+        <v>0.8603</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>589462215</v>
+        <v>501135985</v>
       </c>
       <c r="B92" t="n">
-        <v>182495378879</v>
+        <v>175381179151</v>
       </c>
       <c r="C92" t="n">
-        <v>309.6</v>
+        <v>350</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9155</v>
+        <v>0.8796</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>592801414</v>
+        <v>510640280</v>
       </c>
       <c r="B93" t="n">
-        <v>182673061738</v>
+        <v>177242329304</v>
       </c>
       <c r="C93" t="n">
-        <v>308.2</v>
+        <v>347.1</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9163</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>594731849</v>
+        <v>517349737</v>
       </c>
       <c r="B94" t="n">
-        <v>183021987308</v>
+        <v>177950849866</v>
       </c>
       <c r="C94" t="n">
-        <v>307.7</v>
+        <v>344</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9181</v>
+        <v>0.8925999999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>595560338</v>
+        <v>535975752</v>
       </c>
       <c r="B95" t="n">
-        <v>183092094969</v>
+        <v>178411751519</v>
       </c>
       <c r="C95" t="n">
-        <v>307.4</v>
+        <v>332.9</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9184</v>
+        <v>0.8949</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>596171673</v>
+        <v>539218079</v>
       </c>
       <c r="B96" t="n">
-        <v>183203899441</v>
+        <v>180143531389</v>
       </c>
       <c r="C96" t="n">
-        <v>307.3</v>
+        <v>334.1</v>
       </c>
       <c r="D96" t="n">
-        <v>0.919</v>
+        <v>0.9036</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>601441307</v>
+        <v>551431104</v>
       </c>
       <c r="B97" t="n">
-        <v>183730507870</v>
+        <v>180237578832</v>
       </c>
       <c r="C97" t="n">
-        <v>305.5</v>
+        <v>326.9</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9217</v>
+        <v>0.9041</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>602269795</v>
+        <v>552485769</v>
       </c>
       <c r="B98" t="n">
-        <v>183800615531</v>
+        <v>180332995234</v>
       </c>
       <c r="C98" t="n">
-        <v>305.2</v>
+        <v>326.4</v>
       </c>
       <c r="D98" t="n">
-        <v>0.922</v>
+        <v>0.9045</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>603090822</v>
+        <v>552651220</v>
       </c>
       <c r="B99" t="n">
-        <v>183860341843</v>
+        <v>180346201035</v>
       </c>
       <c r="C99" t="n">
-        <v>304.9</v>
+        <v>326.3</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9223</v>
+        <v>0.9046</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>608283580</v>
+        <v>552816360</v>
       </c>
       <c r="B100" t="n">
-        <v>184258602832</v>
+        <v>180358988177</v>
       </c>
       <c r="C100" t="n">
-        <v>302.9</v>
+        <v>326.3</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9243</v>
+        <v>0.9046999999999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>621716721</v>
+        <v>553867519</v>
       </c>
       <c r="B101" t="n">
-        <v>184461272478</v>
+        <v>180449146842</v>
       </c>
       <c r="C101" t="n">
-        <v>296.7</v>
+        <v>325.8</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9253</v>
+        <v>0.9051</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>634006164</v>
+        <v>565821507</v>
       </c>
       <c r="B102" t="n">
-        <v>184748240782</v>
+        <v>181477388259</v>
       </c>
       <c r="C102" t="n">
-        <v>291.4</v>
+        <v>320.7</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9266</v>
+        <v>0.9103</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>638770707</v>
+        <v>569275136</v>
       </c>
       <c r="B103" t="n">
-        <v>184942362628</v>
+        <v>182096817898</v>
       </c>
       <c r="C103" t="n">
-        <v>289.5</v>
+        <v>319.9</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9276</v>
+        <v>0.9134</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>639510121</v>
+        <v>577891529</v>
       </c>
       <c r="B104" t="n">
-        <v>184966958748</v>
+        <v>183119924178</v>
       </c>
       <c r="C104" t="n">
-        <v>289.2</v>
+        <v>316.9</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9277</v>
+        <v>0.9185</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>641858390</v>
+        <v>609712834</v>
       </c>
       <c r="B105" t="n">
-        <v>185015819043</v>
+        <v>185240939938</v>
       </c>
       <c r="C105" t="n">
-        <v>288.3</v>
+        <v>303.8</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>644768157</v>
+        <v>619217128</v>
       </c>
       <c r="B106" t="n">
-        <v>185108545563</v>
+        <v>187102090091</v>
       </c>
       <c r="C106" t="n">
-        <v>287.1</v>
+        <v>302.2</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9284</v>
+        <v>0.9385</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>647459674</v>
+        <v>625926586</v>
       </c>
       <c r="B107" t="n">
-        <v>186685528990</v>
+        <v>187810610653</v>
       </c>
       <c r="C107" t="n">
-        <v>288.3</v>
+        <v>300.1</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9364</v>
+        <v>0.9421</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>661378463</v>
+        <v>635552951</v>
       </c>
       <c r="B108" t="n">
-        <v>187159640271</v>
+        <v>187839342329</v>
       </c>
       <c r="C108" t="n">
-        <v>283</v>
+        <v>295.6</v>
       </c>
       <c r="D108" t="n">
-        <v>0.9387</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>668696871</v>
+        <v>639254857</v>
       </c>
       <c r="B109" t="n">
-        <v>189958074912</v>
+        <v>187842975760</v>
       </c>
       <c r="C109" t="n">
-        <v>284.1</v>
+        <v>293.8</v>
       </c>
       <c r="D109" t="n">
-        <v>0.9528</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>678201166</v>
+        <v>639359727</v>
       </c>
       <c r="B110" t="n">
-        <v>191819225065</v>
+        <v>188013280298</v>
       </c>
       <c r="C110" t="n">
-        <v>282.8</v>
+        <v>294.1</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9431</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>684910624</v>
+        <v>640793664</v>
       </c>
       <c r="B111" t="n">
-        <v>192527745627</v>
+        <v>188153386789</v>
       </c>
       <c r="C111" t="n">
-        <v>281.1</v>
+        <v>293.6</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9657</v>
+        <v>0.9438</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>698343765</v>
+        <v>641848329</v>
       </c>
       <c r="B112" t="n">
-        <v>192730415273</v>
+        <v>188248803190</v>
       </c>
       <c r="C112" t="n">
-        <v>276</v>
+        <v>293.3</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9668</v>
+        <v>0.9443</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>764975627</v>
+        <v>642013780</v>
       </c>
       <c r="B113" t="n">
-        <v>192778167539</v>
+        <v>188262008991</v>
       </c>
       <c r="C113" t="n">
-        <v>252</v>
+        <v>293.2</v>
       </c>
       <c r="D113" t="n">
-        <v>0.967</v>
+        <v>0.9443</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>766879363</v>
+        <v>642178919</v>
       </c>
       <c r="B114" t="n">
-        <v>195667613062</v>
+        <v>188274796133</v>
       </c>
       <c r="C114" t="n">
-        <v>255.1</v>
+        <v>293.2</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>776383657</v>
+        <v>643230079</v>
       </c>
       <c r="B115" t="n">
-        <v>197528763214</v>
+        <v>188364954798</v>
       </c>
       <c r="C115" t="n">
-        <v>254.4</v>
+        <v>292.8</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9908</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>783093115</v>
+        <v>647503122</v>
       </c>
       <c r="B116" t="n">
-        <v>198237283776</v>
+        <v>188861907350</v>
       </c>
       <c r="C116" t="n">
-        <v>253.1</v>
+        <v>291.7</v>
       </c>
       <c r="D116" t="n">
-        <v>0.9943</v>
+        <v>0.9474</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>796263402</v>
+        <v>648557787</v>
       </c>
       <c r="B117" t="n">
-        <v>199368471000</v>
+        <v>188957323752</v>
       </c>
       <c r="C117" t="n">
-        <v>250.4</v>
+        <v>291.4</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>0.9479</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>931963425</v>
+        <v>648723238</v>
       </c>
       <c r="B118" t="n">
-        <v>200529440906</v>
+        <v>188970529553</v>
       </c>
       <c r="C118" t="n">
-        <v>215.2</v>
+        <v>291.3</v>
       </c>
       <c r="D118" t="n">
-        <v>1.0058</v>
+        <v>0.9479</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>938672883</v>
+        <v>648888377</v>
       </c>
       <c r="B119" t="n">
-        <v>201237961468</v>
+        <v>188983316695</v>
       </c>
       <c r="C119" t="n">
-        <v>214.4</v>
+        <v>291.2</v>
       </c>
       <c r="D119" t="n">
-        <v>1.0094</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>946005586</v>
+        <v>649939536</v>
       </c>
       <c r="B120" t="n">
-        <v>202355312466</v>
+        <v>189073475360</v>
       </c>
       <c r="C120" t="n">
-        <v>213.9</v>
+        <v>290.9</v>
       </c>
       <c r="D120" t="n">
-        <v>1.015</v>
+        <v>0.9484</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>959438727</v>
+        <v>658637696</v>
       </c>
       <c r="B121" t="n">
-        <v>202557982112</v>
+        <v>190012625854</v>
       </c>
       <c r="C121" t="n">
-        <v>211.1</v>
+        <v>288.5</v>
       </c>
       <c r="D121" t="n">
-        <v>1.016</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1101585354</v>
+        <v>665347154</v>
       </c>
       <c r="B122" t="n">
-        <v>205355990158</v>
+        <v>190721146416</v>
       </c>
       <c r="C122" t="n">
-        <v>186.4</v>
+        <v>286.6</v>
       </c>
       <c r="D122" t="n">
-        <v>1.03</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1115018495</v>
+        <v>678780295</v>
       </c>
       <c r="B123" t="n">
-        <v>205558659804</v>
+        <v>190923816062</v>
       </c>
       <c r="C123" t="n">
-        <v>184.4</v>
+        <v>281.3</v>
       </c>
       <c r="D123" t="n">
-        <v>1.031</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1122253479</v>
+        <v>749791564</v>
       </c>
       <c r="B124" t="n">
-        <v>205874327501</v>
+        <v>190972394692</v>
       </c>
       <c r="C124" t="n">
-        <v>183.4</v>
+        <v>254.7</v>
       </c>
       <c r="D124" t="n">
-        <v>1.0326</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1131786994</v>
+        <v>756501022</v>
       </c>
       <c r="B125" t="n">
-        <v>206006069156</v>
+        <v>191680915253</v>
       </c>
       <c r="C125" t="n">
-        <v>182</v>
+        <v>253.4</v>
       </c>
       <c r="D125" t="n">
-        <v>1.0333</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1246058321</v>
+        <v>769934163</v>
       </c>
       <c r="B126" t="n">
-        <v>207714368611</v>
+        <v>191883584899</v>
       </c>
       <c r="C126" t="n">
-        <v>166.7</v>
+        <v>249.2</v>
       </c>
       <c r="D126" t="n">
-        <v>1.0419</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1255591836</v>
+        <v>776494259</v>
       </c>
       <c r="B127" t="n">
-        <v>207846110266</v>
+        <v>192257449912</v>
       </c>
       <c r="C127" t="n">
-        <v>165.5</v>
+        <v>247.6</v>
       </c>
       <c r="D127" t="n">
-        <v>1.0425</v>
+        <v>0.9643</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1390899429</v>
+        <v>780049650</v>
       </c>
       <c r="B128" t="n">
-        <v>207952304090</v>
+        <v>196798800285</v>
       </c>
       <c r="C128" t="n">
-        <v>149.5</v>
+        <v>252.3</v>
       </c>
       <c r="D128" t="n">
-        <v>1.043</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1400432944</v>
+        <v>789553944</v>
       </c>
       <c r="B129" t="n">
-        <v>208084045745</v>
+        <v>198659950438</v>
       </c>
       <c r="C129" t="n">
-        <v>148.6</v>
+        <v>251.6</v>
       </c>
       <c r="D129" t="n">
-        <v>1.0437</v>
+        <v>0.9964</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1514704271</v>
+        <v>796263402</v>
       </c>
       <c r="B130" t="n">
-        <v>209792345200</v>
+        <v>199368471000</v>
       </c>
       <c r="C130" t="n">
-        <v>138.5</v>
+        <v>250.4</v>
       </c>
       <c r="D130" t="n">
-        <v>1.0523</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1524237786</v>
+        <v>809696543</v>
       </c>
       <c r="B131" t="n">
-        <v>209924086855</v>
+        <v>199571140646</v>
       </c>
       <c r="C131" t="n">
-        <v>137.7</v>
+        <v>246.5</v>
       </c>
       <c r="D131" t="n">
-        <v>1.0529</v>
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>897331728</v>
+      </c>
+      <c r="B132" t="n">
+        <v>201370336139</v>
+      </c>
+      <c r="C132" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>904041186</v>
+      </c>
+      <c r="B133" t="n">
+        <v>202078856700</v>
+      </c>
+      <c r="C133" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.0136</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>917474327</v>
+      </c>
+      <c r="B134" t="n">
+        <v>202281526346</v>
+      </c>
+      <c r="C134" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.0146</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>939010743</v>
+      </c>
+      <c r="B135" t="n">
+        <v>202356595348</v>
+      </c>
+      <c r="C135" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.015</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1026645929</v>
+      </c>
+      <c r="B136" t="n">
+        <v>204155790841</v>
+      </c>
+      <c r="C136" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1033355386</v>
+      </c>
+      <c r="B137" t="n">
+        <v>204864311403</v>
+      </c>
+      <c r="C137" t="n">
+        <v>198.3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.0276</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1046788527</v>
+      </c>
+      <c r="B138" t="n">
+        <v>205066981049</v>
+      </c>
+      <c r="C138" t="n">
+        <v>195.9</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.0286</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1126341364</v>
+      </c>
+      <c r="B139" t="n">
+        <v>205927253572</v>
+      </c>
+      <c r="C139" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.0329</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1131103073</v>
+      </c>
+      <c r="B140" t="n">
+        <v>206387814260</v>
+      </c>
+      <c r="C140" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.0352</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1140636589</v>
+      </c>
+      <c r="B141" t="n">
+        <v>206519555915</v>
+      </c>
+      <c r="C141" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1.0359</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1209704198</v>
+      </c>
+      <c r="B142" t="n">
+        <v>207131404782</v>
+      </c>
+      <c r="C142" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.0389</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1214465907</v>
+      </c>
+      <c r="B143" t="n">
+        <v>207591965469</v>
+      </c>
+      <c r="C143" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1.0413</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1223999423</v>
+      </c>
+      <c r="B144" t="n">
+        <v>207723707124</v>
+      </c>
+      <c r="C144" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.0419</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1356407714</v>
+      </c>
+      <c r="B145" t="n">
+        <v>207856500229</v>
+      </c>
+      <c r="C145" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.0426</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1361169424</v>
+      </c>
+      <c r="B146" t="n">
+        <v>208317060917</v>
+      </c>
+      <c r="C146" t="n">
+        <v>153</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.0449</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1370702939</v>
+      </c>
+      <c r="B147" t="n">
+        <v>208448802572</v>
+      </c>
+      <c r="C147" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1.0455</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1439770548</v>
+      </c>
+      <c r="B148" t="n">
+        <v>209060651439</v>
+      </c>
+      <c r="C148" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.0486</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1444532258</v>
+      </c>
+      <c r="B149" t="n">
+        <v>209521212126</v>
+      </c>
+      <c r="C149" t="n">
+        <v>145</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1.0509</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1454065773</v>
+      </c>
+      <c r="B150" t="n">
+        <v>209652953782</v>
+      </c>
+      <c r="C150" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1.0516</v>
       </c>
     </row>
   </sheetData>
